--- a/results/job_matches_2026-03-21.xlsx
+++ b/results/job_matches_2026-03-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. GenAI Engineer</t>
+          <t>System Architect – Database Focus</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Walpole, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,69 +1116,69 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, MySQL, MongoDB, NoSQL, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f37a180376834e2</t>
+          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>System Architect – Database Focus</t>
+          <t>Software Engineer II_AI/ML</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Walpole, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f638e48249099e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer II_AI/ML</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Coastal Credit Union</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f638e48249099e</t>
+          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Coastal Credit Union</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
+          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
+          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
+          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Cambium Learning Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
+          <t>https://www.indeed.com/viewjob?jk=c674b29c5cebe1e7</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Part-Time Data Ingest Engineer (contractor)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Digital Public Library of America</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
+          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
+          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Harvestaff</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10432e8c7b264b93</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Snap Inc.</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
+          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QA Testing Analyst - Senior</t>
+          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Snap Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
+          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Engineer Senior</t>
+          <t>QA Testing Analyst - Senior</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
+          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>AI Engineer Senior</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
+          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
         </is>
       </c>
     </row>
@@ -1786,29 +1786,29 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
+          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AWS Solution Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, Zookeeper, Scala, Kafka, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ebb6287ea5ed18b</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Cybersecurity Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Platform Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
+          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>La Mesa RV Center</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
+          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Support Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
+          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e599db25edc63644</t>
+          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b05ba4615bbc0</t>
+          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Oracle DBA - OCI</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea7797a2adda23</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer / SDE</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
+          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Murmuration</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
+          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - California</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36f86f8a126e87b</t>
+          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java Full Stack</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer II - IM Enterprise Data</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CHRISTUS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
+          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps/Platform Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
+          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
+          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Java Python Full Stack Developer Associate Software Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
+          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Teza Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
+          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>IonQ</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
+          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Architect - Data Lake &amp; Data Engineering</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
+          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,102 +2736,102 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Curana Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
+          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,40 +2841,4100 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Fresno, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>AWS Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Chandler, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, Zookeeper, Scala, Kafka, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ebb6287ea5ed18b</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Cloud Data Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Barclays</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Whippany, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Data &amp; AI Platform Data Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5bda9e48f1024e1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fd1e9c1ff303313</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=572dd86ccc7be082</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c071e49659e50353</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56d3332bdc3b7e53</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9127aed6ba1f03c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3d981d1c9de85b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20ecba012dcb872c</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c50789f60821a3d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5db3e8ec7e08e1e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04ae245d423f4f15</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=400f98db4bb6f73d</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=555e2360433f2c3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f40885146dec8a4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d5035a08ea5f1e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6606e12c9ff1b3b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4009b2546e8fe076</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac7f86149a2ec340</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d56d5772e687db6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50c3341377ed57a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9f65756a24c765f</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=666278eb7c24f496</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77709f84c9c6155a</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=280432393e5a110e</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e86adf0022116a65</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e612de3275e3115</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=677d6d574c5b3ec3</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5466c81ac58d34ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b330ccc7aa453c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a26e11c7ee167aed</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ec69fe49ff8d9dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=126ea7cdef071597</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73105a0a5b0d4d0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48cce4424eee2763</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eeff413ec474b08b</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Midland, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8af2618770b10440</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50b3e493edc2083f</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba3bf92b7f61bf8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7383fef92c3e822c</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46c1031df8a5a78f</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24a79838f620ae29</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff04d88198df5a34</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=801eb4fb019f4e56</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1756687393957d87</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a51ae7d37b780a38</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6a6987c98089cbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0cca6c31994af17d</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75d7d20700151ded</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c6fa018886126e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43627fd85a12efa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84ae12f4cb92ce29</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Fresno, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=662d5c581b3eff4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51d6fa2517837adc</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b66be563d1df5434</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c258712e0383042</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc2b6b27a7b388ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30f6e0934dbdb9a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b9fddf6b4dcba23</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Application Architect</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b06cd6e272dc273</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Sr Python Developer - Onsite</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>M-TECH SYSTEMS</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Dunwoody, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Solution Architect</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>La Mesa RV Center</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Makpar Corporation</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CloudFormation, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=644ffd1ada2946fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>HealthMark Group</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Senior Support Engineer</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Lyric</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Senior Data Platform Engineer / SDE</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Cambia Health Solutions</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Senior QA Engineer</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Murmuration</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>BAE Systems USA</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Rockville, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer, Java Full Stack</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Data Analytics Engineer II - IM Enterprise Data</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>CHRISTUS Health</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>DevOps/Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Java Python Full Stack Developer Associate Software Engineer</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Data Architect - Data Lake &amp; Data Engineering</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Curana Health</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>AI Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Doral, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Teza Technologies</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>IonQ</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Bothell, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Mexico, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
           <t>Business Intelligence Developer</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B185" t="inlineStr">
         <is>
           <t>ICF</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C185" t="inlineStr">
         <is>
           <t>Reston, VA, US USA</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D185" t="n">
         <v>10.4</v>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E185" t="inlineStr">
         <is>
           <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>ICF</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c2b1378a08eea421</t>
         </is>

--- a/results/job_matches_2026-03-21.xlsx
+++ b/results/job_matches_2026-03-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G186"/>
+  <dimension ref="A1:G192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – CDO / Data &amp; AI Engineering</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Spark Streaming, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,164 +496,164 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c03da34050d1fb85</t>
+          <t>https://www.indeed.com/viewjob?jk=1a791d73f0d13a4b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, DynamoDB</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fecb0cbc521360f</t>
+          <t>https://www.indeed.com/viewjob?jk=036c0aeccda18107</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
+          <t>Senior Data Engineer – CDO / Data &amp; AI Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Spark Streaming, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1204728c106ec46</t>
+          <t>https://www.indeed.com/viewjob?jk=c03da34050d1fb85</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d64ff1548d48cfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=1fecb0cbc521360f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Kubernetes Engineer</t>
+          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Northcross Group</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Marquette, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f734c7c5315c58</t>
+          <t>https://www.indeed.com/viewjob?jk=d1204728c106ec46</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Kubernetes Engineer</t>
+          <t>Python and PySpark, No SQL Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Northcross Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b0cc109a6bef88b</t>
+          <t>https://www.indeed.com/viewjob?jk=d64ff1548d48cfe8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>AWS Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Northcross Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Marquette, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2163f01dd05b34</t>
+          <t>https://www.indeed.com/viewjob?jk=15f734c7c5315c58</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote, US)</t>
+          <t>AWS Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>Northcross Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d18e2b948851633</t>
+          <t>https://www.indeed.com/viewjob?jk=3b0cc109a6bef88b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Platform and Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AMETEK</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Berwyn, PA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7257366c07155d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2163f01dd05b34</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Openly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e13bcfee6252358d</t>
+          <t>https://www.indeed.com/viewjob?jk=4d18e2b948851633</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hadoop, Spark, PySpark, Snowflake, Oracle</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e5351d1c126599</t>
+          <t>https://www.indeed.com/viewjob?jk=e13bcfee6252358d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Solutions Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hadoop, Spark, PySpark, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e5351d1c126599</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
+          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer-60009025</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>State of South Carolina</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,69 +976,69 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
+          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer-60009025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CNC Software</t>
+          <t>State of South Carolina</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
+          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer III (SWES03) DT_AI/ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CNC Software</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software Engineer III (SWES03) DT_AI/ML</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cooper Standard</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Northville, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=419f48f4c723af35</t>
+          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>System Architect – Database Focus</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>Cooper Standard</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Walpole, MA, US USA</t>
+          <t>Northville, MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
+          <t>https://www.indeed.com/viewjob?jk=419f48f4c723af35</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer II_AI/ML</t>
+          <t>System Architect – Database Focus</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Walpole, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f638e48249099e</t>
+          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Coastal Credit Union</t>
+          <t>Independence Pet Holdings</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a6d5ce748599c6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer II_AI/ML</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f638e48249099e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Coastal Credit Union</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
+          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
+          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cambium Learning Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c674b29c5cebe1e7</t>
+          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
+          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ENGINEER (REMOTE OPPORTUNITY)</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Cambium Learning Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bed15d2d90e0d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=c674b29c5cebe1e7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer-Data Platform &amp; Analytics</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177880cf8dc57acd</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>SENIOR PRODUCT ENGINEER (REMOTE OPPORTUNITY)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
+          <t>https://www.indeed.com/viewjob?jk=2bed15d2d90e0d1d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Software Developer</t>
+          <t>Data Engineer-Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
+          <t>https://www.indeed.com/viewjob?jk=177880cf8dc57acd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Part-Time Data Ingest Engineer (contractor)</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Digital Public Library of America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
+          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Harvestaff</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
+          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Part-Time Data Ingest Engineer (contractor)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Digital Public Library of America</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
+          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
+          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Snap Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>QA Testing Analyst - Senior</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Harvestaff</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Engineer Senior</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
+          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Snap Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,59 +1791,59 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
+          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>QA Testing Analyst - Senior</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
+          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cybersecurity Data Engineer</t>
+          <t>AI Engineer Senior</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
+          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
+          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Cybersecurity Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DevCo Management</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
+          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
+          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
+          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
+          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
+          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
+          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
+          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
+          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
+          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
+          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
+          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
+          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
+          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
+          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
+          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
+          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
+          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
+          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
+          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
+          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
+          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
+          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
+          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
+          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
+          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
+          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
+          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
+          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
+          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
+          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
+          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
+          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AWS Solution Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, Zookeeper, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ebb6287ea5ed18b</t>
+          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
+          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Platform Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,24 +3986,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
+          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bda9e48f1024e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>AWS Solution Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, Zookeeper, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd1e9c1ff303313</t>
+          <t>https://www.indeed.com/viewjob?jk=9ebb6287ea5ed18b</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572dd86ccc7be082</t>
+          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Senior Data &amp; AI Platform Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c071e49659e50353</t>
+          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d3332bdc3b7e53</t>
+          <t>https://www.indeed.com/viewjob?jk=5bda9e48f1024e1e</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9127aed6ba1f03c6</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd1e9c1ff303313</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d981d1c9de85b5</t>
+          <t>https://www.indeed.com/viewjob?jk=572dd86ccc7be082</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ecba012dcb872c</t>
+          <t>https://www.indeed.com/viewjob?jk=c071e49659e50353</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50789f60821a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=56d3332bdc3b7e53</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5db3e8ec7e08e1e1</t>
+          <t>https://www.indeed.com/viewjob?jk=9127aed6ba1f03c6</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04ae245d423f4f15</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d981d1c9de85b5</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=400f98db4bb6f73d</t>
+          <t>https://www.indeed.com/viewjob?jk=20ecba012dcb872c</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555e2360433f2c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=c50789f60821a3d7</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40885146dec8a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=5db3e8ec7e08e1e1</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5035a08ea5f1e7</t>
+          <t>https://www.indeed.com/viewjob?jk=04ae245d423f4f15</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6606e12c9ff1b3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=400f98db4bb6f73d</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4009b2546e8fe076</t>
+          <t>https://www.indeed.com/viewjob?jk=555e2360433f2c3d</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac7f86149a2ec340</t>
+          <t>https://www.indeed.com/viewjob?jk=f40885146dec8a4b</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56d5772e687db6e</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5035a08ea5f1e7</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c3341377ed57a3</t>
+          <t>https://www.indeed.com/viewjob?jk=6606e12c9ff1b3b4</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f65756a24c765f</t>
+          <t>https://www.indeed.com/viewjob?jk=4009b2546e8fe076</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=666278eb7c24f496</t>
+          <t>https://www.indeed.com/viewjob?jk=ac7f86149a2ec340</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77709f84c9c6155a</t>
+          <t>https://www.indeed.com/viewjob?jk=d56d5772e687db6e</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=280432393e5a110e</t>
+          <t>https://www.indeed.com/viewjob?jk=50c3341377ed57a3</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e86adf0022116a65</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f65756a24c765f</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e612de3275e3115</t>
+          <t>https://www.indeed.com/viewjob?jk=666278eb7c24f496</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677d6d574c5b3ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=77709f84c9c6155a</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5466c81ac58d34ff</t>
+          <t>https://www.indeed.com/viewjob?jk=280432393e5a110e</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b330ccc7aa453c5</t>
+          <t>https://www.indeed.com/viewjob?jk=e86adf0022116a65</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a26e11c7ee167aed</t>
+          <t>https://www.indeed.com/viewjob?jk=6e612de3275e3115</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec69fe49ff8d9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=677d6d574c5b3ec3</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126ea7cdef071597</t>
+          <t>https://www.indeed.com/viewjob?jk=5466c81ac58d34ff</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73105a0a5b0d4d0a</t>
+          <t>https://www.indeed.com/viewjob?jk=5b330ccc7aa453c5</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48cce4424eee2763</t>
+          <t>https://www.indeed.com/viewjob?jk=a26e11c7ee167aed</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeff413ec474b08b</t>
+          <t>https://www.indeed.com/viewjob?jk=2ec69fe49ff8d9dd</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8af2618770b10440</t>
+          <t>https://www.indeed.com/viewjob?jk=126ea7cdef071597</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b3e493edc2083f</t>
+          <t>https://www.indeed.com/viewjob?jk=73105a0a5b0d4d0a</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3bf92b7f61bf8b</t>
+          <t>https://www.indeed.com/viewjob?jk=48cce4424eee2763</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7383fef92c3e822c</t>
+          <t>https://www.indeed.com/viewjob?jk=eeff413ec474b08b</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46c1031df8a5a78f</t>
+          <t>https://www.indeed.com/viewjob?jk=8af2618770b10440</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a79838f620ae29</t>
+          <t>https://www.indeed.com/viewjob?jk=50b3e493edc2083f</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff04d88198df5a34</t>
+          <t>https://www.indeed.com/viewjob?jk=ba3bf92b7f61bf8b</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=801eb4fb019f4e56</t>
+          <t>https://www.indeed.com/viewjob?jk=7383fef92c3e822c</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1756687393957d87</t>
+          <t>https://www.indeed.com/viewjob?jk=46c1031df8a5a78f</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a51ae7d37b780a38</t>
+          <t>https://www.indeed.com/viewjob?jk=24a79838f620ae29</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a6987c98089cbb</t>
+          <t>https://www.indeed.com/viewjob?jk=ff04d88198df5a34</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cca6c31994af17d</t>
+          <t>https://www.indeed.com/viewjob?jk=801eb4fb019f4e56</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d7d20700151ded</t>
+          <t>https://www.indeed.com/viewjob?jk=1756687393957d87</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6fa018886126e9</t>
+          <t>https://www.indeed.com/viewjob?jk=a51ae7d37b780a38</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43627fd85a12efa0</t>
+          <t>https://www.indeed.com/viewjob?jk=e6a6987c98089cbb</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ae12f4cb92ce29</t>
+          <t>https://www.indeed.com/viewjob?jk=0cca6c31994af17d</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=662d5c581b3eff4c</t>
+          <t>https://www.indeed.com/viewjob?jk=75d7d20700151ded</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51d6fa2517837adc</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6fa018886126e9</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b66be563d1df5434</t>
+          <t>https://www.indeed.com/viewjob?jk=43627fd85a12efa0</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c258712e0383042</t>
+          <t>https://www.indeed.com/viewjob?jk=84ae12f4cb92ce29</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2b6b27a7b388ce</t>
+          <t>https://www.indeed.com/viewjob?jk=662d5c581b3eff4c</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f6e0934dbdb9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=51d6fa2517837adc</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,14 +6026,14 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9fddf6b4dcba23</t>
+          <t>https://www.indeed.com/viewjob?jk=b66be563d1df5434</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Application Architect</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b06cd6e272dc273</t>
+          <t>https://www.indeed.com/viewjob?jk=4c258712e0383042</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=dc2b6b27a7b388ce</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>La Mesa RV Center</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
+          <t>https://www.indeed.com/viewjob?jk=30f6e0934dbdb9a0</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Makpar Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,24 +6166,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=644ffd1ada2946fd</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9fddf6b4dcba23</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Application Architect</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
+          <t>https://www.indeed.com/viewjob?jk=4b06cd6e272dc273</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Python Developer - Onsite</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>La Mesa RV Center</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Senior Support Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer / SDE</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,34 +6331,34 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Murmuration</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,32 +6376,32 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Support Engineer</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,102 +6411,102 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java Full Stack</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
+          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer II - IM Enterprise Data</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>CHRISTUS Health</t>
+          <t>Murmuration</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
+          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>DevOps/Platform Engineer</t>
+          <t>APIGEE Development Engineer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6516,32 +6516,32 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
+          <t>https://www.indeed.com/viewjob?jk=fce9a26ec94275c2</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Makpar Corporation</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,24 +6551,24 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
+          <t>https://www.indeed.com/viewjob?jk=644ffd1ada2946fd</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Java Python Full Stack Developer Associate Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,24 +6586,24 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
+          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
+          <t>Sr. Software Engineer, Java Full Stack</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,24 +6621,24 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Data Analytics Engineer II - IM Enterprise Data</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CHRISTUS Health</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,34 +6646,34 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
+          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Data Architect - Data Lake &amp; Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Redwood Trust</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,34 +6681,34 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
+          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps/Platform Engineer</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Curana Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,34 +6716,34 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
+          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer</t>
+          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,34 +6751,34 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Java Python Full Stack Developer Associate Software Engineer</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Teza Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,24 +6796,24 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
+          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
+          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>IonQ</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6831,24 +6831,24 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
+          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6866,24 +6866,24 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
+          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Data Architect - Data Lake &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6901,24 +6901,24 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
+          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Curana Health</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,15 +6926,225 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>AI Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Doral, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Teza Technologies</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>IonQ</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Bothell, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Mexico, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>ICF</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
           <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>ICF</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c2b1378a08eea421</t>
         </is>

--- a/results/job_matches_2026-03-21.xlsx
+++ b/results/job_matches_2026-03-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G192"/>
+  <dimension ref="A1:G196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CNC Software</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
+          <t>https://www.indeed.com/viewjob?jk=3b81ca9e34e5e9f1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer III (SWES03) DT_AI/ML</t>
+          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=520c71629e4ae31f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cooper Standard</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Northville, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=419f48f4c723af35</t>
+          <t>https://www.indeed.com/viewjob?jk=96b820a060e96568</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>System Architect – Database Focus</t>
+          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Walpole, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce993d8d61236e3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Independence Pet Holdings</t>
+          <t>CNC Software</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a6d5ce748599c6</t>
+          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer II_AI/ML</t>
+          <t>Software Engineer III (SWES03) DT_AI/ML</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1231,94 +1231,94 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f638e48249099e</t>
+          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Coastal Credit Union</t>
+          <t>Cooper Standard</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Northville, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
+          <t>https://www.indeed.com/viewjob?jk=419f48f4c723af35</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>System Architect – Database Focus</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Walpole, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
+          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Independence Pet Holdings</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a6d5ce748599c6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>Software Engineer II_AI/ML</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f638e48249099e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cambium Learning Group</t>
+          <t>Coastal Credit Union</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c674b29c5cebe1e7</t>
+          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
+          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ENGINEER (REMOTE OPPORTUNITY)</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bed15d2d90e0d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer-Data Platform &amp; Analytics</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177880cf8dc57acd</t>
+          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cambium Learning Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
+          <t>https://www.indeed.com/viewjob?jk=c674b29c5cebe1e7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Software Developer</t>
+          <t>SENIOR PRODUCT ENGINEER (REMOTE OPPORTUNITY)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
+          <t>https://www.indeed.com/viewjob?jk=2bed15d2d90e0d1d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,59 +1616,59 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Part-Time Data Ingest Engineer (contractor)</t>
+          <t>Software Engineers</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Digital Public Library of America</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Roseland, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, RDS, Scala, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
+          <t>https://www.indeed.com/viewjob?jk=bb04b36537a2b802</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
+          <t>Data Engineer-Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
+          <t>https://www.indeed.com/viewjob?jk=177880cf8dc57acd</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Harvestaff</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Sr Software Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
+          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
+          <t>Part-Time Data Ingest Engineer (contractor)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Snap Inc.</t>
+          <t>Digital Public Library of America</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
+          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QA Testing Analyst - Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
+          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Engineer Senior</t>
+          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Harvestaff</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,102 +1896,102 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
+          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cybersecurity Data Engineer</t>
+          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Snap Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
+          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>QA Testing Analyst - Senior</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DevCo Management</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>AI Engineer Senior</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
+          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
+          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Cybersecurity Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DevCo Management</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
+          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
+          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
+          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
+          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
+          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
+          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
+          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
+          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
+          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
+          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
+          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
+          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
+          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
+          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
+          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
+          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
+          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
+          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
+          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
+          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
+          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
+          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
+          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
+          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
+          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
+          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
+          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
+          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
+          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
+          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
+          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
+          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
+          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AWS Solution Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, Zookeeper, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ebb6287ea5ed18b</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
+          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Platform Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,24 +4126,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
+          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,14 +4171,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bda9e48f1024e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd1e9c1ff303313</t>
+          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>AWS Solution Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, Zookeeper, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572dd86ccc7be082</t>
+          <t>https://www.indeed.com/viewjob?jk=9ebb6287ea5ed18b</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c071e49659e50353</t>
+          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Senior Data &amp; AI Platform Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,17 +4301,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d3332bdc3b7e53</t>
+          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9127aed6ba1f03c6</t>
+          <t>https://www.indeed.com/viewjob?jk=5bda9e48f1024e1e</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d981d1c9de85b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd1e9c1ff303313</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ecba012dcb872c</t>
+          <t>https://www.indeed.com/viewjob?jk=572dd86ccc7be082</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50789f60821a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c071e49659e50353</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5db3e8ec7e08e1e1</t>
+          <t>https://www.indeed.com/viewjob?jk=56d3332bdc3b7e53</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04ae245d423f4f15</t>
+          <t>https://www.indeed.com/viewjob?jk=9127aed6ba1f03c6</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=400f98db4bb6f73d</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d981d1c9de85b5</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555e2360433f2c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=20ecba012dcb872c</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40885146dec8a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=c50789f60821a3d7</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5035a08ea5f1e7</t>
+          <t>https://www.indeed.com/viewjob?jk=5db3e8ec7e08e1e1</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6606e12c9ff1b3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=04ae245d423f4f15</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4009b2546e8fe076</t>
+          <t>https://www.indeed.com/viewjob?jk=400f98db4bb6f73d</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac7f86149a2ec340</t>
+          <t>https://www.indeed.com/viewjob?jk=555e2360433f2c3d</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56d5772e687db6e</t>
+          <t>https://www.indeed.com/viewjob?jk=f40885146dec8a4b</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c3341377ed57a3</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5035a08ea5f1e7</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f65756a24c765f</t>
+          <t>https://www.indeed.com/viewjob?jk=6606e12c9ff1b3b4</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=666278eb7c24f496</t>
+          <t>https://www.indeed.com/viewjob?jk=4009b2546e8fe076</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77709f84c9c6155a</t>
+          <t>https://www.indeed.com/viewjob?jk=ac7f86149a2ec340</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=280432393e5a110e</t>
+          <t>https://www.indeed.com/viewjob?jk=d56d5772e687db6e</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e86adf0022116a65</t>
+          <t>https://www.indeed.com/viewjob?jk=50c3341377ed57a3</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e612de3275e3115</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f65756a24c765f</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677d6d574c5b3ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=666278eb7c24f496</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5466c81ac58d34ff</t>
+          <t>https://www.indeed.com/viewjob?jk=77709f84c9c6155a</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b330ccc7aa453c5</t>
+          <t>https://www.indeed.com/viewjob?jk=280432393e5a110e</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a26e11c7ee167aed</t>
+          <t>https://www.indeed.com/viewjob?jk=e86adf0022116a65</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec69fe49ff8d9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=6e612de3275e3115</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126ea7cdef071597</t>
+          <t>https://www.indeed.com/viewjob?jk=677d6d574c5b3ec3</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73105a0a5b0d4d0a</t>
+          <t>https://www.indeed.com/viewjob?jk=5466c81ac58d34ff</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48cce4424eee2763</t>
+          <t>https://www.indeed.com/viewjob?jk=5b330ccc7aa453c5</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeff413ec474b08b</t>
+          <t>https://www.indeed.com/viewjob?jk=a26e11c7ee167aed</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8af2618770b10440</t>
+          <t>https://www.indeed.com/viewjob?jk=2ec69fe49ff8d9dd</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b3e493edc2083f</t>
+          <t>https://www.indeed.com/viewjob?jk=126ea7cdef071597</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3bf92b7f61bf8b</t>
+          <t>https://www.indeed.com/viewjob?jk=73105a0a5b0d4d0a</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7383fef92c3e822c</t>
+          <t>https://www.indeed.com/viewjob?jk=48cce4424eee2763</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46c1031df8a5a78f</t>
+          <t>https://www.indeed.com/viewjob?jk=eeff413ec474b08b</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a79838f620ae29</t>
+          <t>https://www.indeed.com/viewjob?jk=8af2618770b10440</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff04d88198df5a34</t>
+          <t>https://www.indeed.com/viewjob?jk=50b3e493edc2083f</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=801eb4fb019f4e56</t>
+          <t>https://www.indeed.com/viewjob?jk=ba3bf92b7f61bf8b</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1756687393957d87</t>
+          <t>https://www.indeed.com/viewjob?jk=7383fef92c3e822c</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a51ae7d37b780a38</t>
+          <t>https://www.indeed.com/viewjob?jk=46c1031df8a5a78f</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a6987c98089cbb</t>
+          <t>https://www.indeed.com/viewjob?jk=24a79838f620ae29</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cca6c31994af17d</t>
+          <t>https://www.indeed.com/viewjob?jk=ff04d88198df5a34</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d7d20700151ded</t>
+          <t>https://www.indeed.com/viewjob?jk=801eb4fb019f4e56</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6fa018886126e9</t>
+          <t>https://www.indeed.com/viewjob?jk=1756687393957d87</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43627fd85a12efa0</t>
+          <t>https://www.indeed.com/viewjob?jk=a51ae7d37b780a38</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ae12f4cb92ce29</t>
+          <t>https://www.indeed.com/viewjob?jk=e6a6987c98089cbb</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=662d5c581b3eff4c</t>
+          <t>https://www.indeed.com/viewjob?jk=0cca6c31994af17d</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51d6fa2517837adc</t>
+          <t>https://www.indeed.com/viewjob?jk=75d7d20700151ded</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b66be563d1df5434</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6fa018886126e9</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c258712e0383042</t>
+          <t>https://www.indeed.com/viewjob?jk=43627fd85a12efa0</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2b6b27a7b388ce</t>
+          <t>https://www.indeed.com/viewjob?jk=84ae12f4cb92ce29</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f6e0934dbdb9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=662d5c581b3eff4c</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,14 +6166,14 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9fddf6b4dcba23</t>
+          <t>https://www.indeed.com/viewjob?jk=51d6fa2517837adc</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Application Architect</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b06cd6e272dc273</t>
+          <t>https://www.indeed.com/viewjob?jk=b66be563d1df5434</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=4c258712e0383042</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>La Mesa RV Center</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
+          <t>https://www.indeed.com/viewjob?jk=dc2b6b27a7b388ce</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
+          <t>https://www.indeed.com/viewjob?jk=30f6e0934dbdb9a0</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9fddf6b4dcba23</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Application Architect</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,24 +6376,24 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=4b06cd6e272dc273</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Senior Support Engineer</t>
+          <t>Sr Python Developer - Onsite</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
+          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer / SDE</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>La Mesa RV Center</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,29 +6436,29 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Murmuration</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>APIGEE Development Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6516,24 +6516,24 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce9a26ec94275c2</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Makpar Corporation</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,32 +6551,32 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=644ffd1ada2946fd</t>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Support Engineer</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,137 +6586,137 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java Full Stack</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
+          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer II - IM Enterprise Data</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>CHRISTUS Health</t>
+          <t>Murmuration</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
+          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>APIGEE Development Engineer</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Redwood Trust</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
+          <t>https://www.indeed.com/viewjob?jk=fce9a26ec94275c2</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>DevOps/Platform Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Makpar Corporation</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
+          <t>https://www.indeed.com/viewjob?jk=644ffd1ada2946fd</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
+          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Java Python Full Stack Developer Associate Software Engineer</t>
+          <t>Sr. Software Engineer, Java Full Stack</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,24 +6796,24 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
+          <t>Data Analytics Engineer II - IM Enterprise Data</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CHRISTUS Health</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,34 +6821,34 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
+          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Redwood Trust</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,34 +6856,34 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
+          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Data Architect - Data Lake &amp; Data Engineering</t>
+          <t>DevOps/Platform Engineer</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6901,24 +6901,24 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
+          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Curana Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,34 +6926,34 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
+          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer</t>
+          <t>Java Python Full Stack Developer Associate Software Engineer</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,34 +6961,34 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Teza Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7006,24 +7006,24 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
+          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>IonQ</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7041,24 +7041,24 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
+          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Git, Python, SQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7076,24 +7076,24 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bebf82409e7078</t>
+          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>IonQ</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -7111,24 +7111,24 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
+          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Data Architect - Data Lake &amp; Data Engineering</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7136,15 +7136,155 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Curana Health</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>AI Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Doral, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>ICF</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
           <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>ICF</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c2b1378a08eea421</t>
         </is>

--- a/results/job_matches_2026-03-21.xlsx
+++ b/results/job_matches_2026-03-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G196"/>
+  <dimension ref="A1:G192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fecb0cbc521360f</t>
+          <t>https://www.indeed.com/viewjob?jk=d1204728c106ec46</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1204728c106ec46</t>
+          <t>https://www.indeed.com/viewjob?jk=1fecb0cbc521360f</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer II</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hadoop, Spark, PySpark, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e5351d1c126599</t>
+          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
+          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Data Engineer-60009025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>State of South Carolina</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
+          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer-60009025</t>
+          <t>Data Solutions Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>State of South Carolina</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hadoop, Spark, PySpark, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e5351d1c126599</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III (SWES03) DT_AI/ML</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CNC Software</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
+          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer III (SWES03) DT_AI/ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CNC Software</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>SENIOR PRODUCT ENGINEER (REMOTE OPPORTUNITY)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cambium Learning Group</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c674b29c5cebe1e7</t>
+          <t>https://www.indeed.com/viewjob?jk=2bed15d2d90e0d1d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ENGINEER (REMOTE OPPORTUNITY)</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bed15d2d90e0d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>Software Engineers</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Roseland, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,69 +1606,69 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, RDS, Scala, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
+          <t>https://www.indeed.com/viewjob?jk=bb04b36537a2b802</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineers</t>
+          <t>Data Engineer-Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Roseland, NJ, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb04b36537a2b802</t>
+          <t>https://www.indeed.com/viewjob?jk=177880cf8dc57acd</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer-Data Platform &amp; Analytics</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177880cf8dc57acd</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Sr Software Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
+          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Software Developer</t>
+          <t>Part-Time Data Ingest Engineer (contractor)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Digital Public Library of America</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
+          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Part-Time Data Ingest Engineer (contractor)</t>
+          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Digital Public Library of America</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Harvestaff</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08899fe7be35149e</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
+          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Harvestaff</t>
+          <t>Snap Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
+          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>QA Testing Analyst - Senior</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
+          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
+          <t>Cybersecurity Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Snap Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>QA Testing Analyst - Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>DevCo Management</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
+          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Engineer Senior</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
+          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
+          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
+          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cybersecurity Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
+          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DevCo Management</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
+          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
+          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
+          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
+          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
+          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
+          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
+          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
+          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
+          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
+          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
+          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
+          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
+          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
+          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
+          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
+          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
+          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
+          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
+          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
+          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
+          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
+          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
+          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
+          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
+          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
+          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
+          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
+          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
+          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
+          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
+          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
+          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
+          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>AWS Solution Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, Zookeeper, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=9ebb6287ea5ed18b</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
+          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>AI Engineer Senior</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
+          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AWS Solution Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, Zookeeper, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ebb6287ea5ed18b</t>
+          <t>https://www.indeed.com/viewjob?jk=5bda9e48f1024e1e</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd1e9c1ff303313</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Platform Data Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,17 +4301,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, CI/CD, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f8075b573654a6</t>
+          <t>https://www.indeed.com/viewjob?jk=572dd86ccc7be082</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bda9e48f1024e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=c071e49659e50353</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd1e9c1ff303313</t>
+          <t>https://www.indeed.com/viewjob?jk=56d3332bdc3b7e53</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572dd86ccc7be082</t>
+          <t>https://www.indeed.com/viewjob?jk=9127aed6ba1f03c6</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c071e49659e50353</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d981d1c9de85b5</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d3332bdc3b7e53</t>
+          <t>https://www.indeed.com/viewjob?jk=20ecba012dcb872c</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9127aed6ba1f03c6</t>
+          <t>https://www.indeed.com/viewjob?jk=c50789f60821a3d7</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d981d1c9de85b5</t>
+          <t>https://www.indeed.com/viewjob?jk=5db3e8ec7e08e1e1</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ecba012dcb872c</t>
+          <t>https://www.indeed.com/viewjob?jk=04ae245d423f4f15</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50789f60821a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=400f98db4bb6f73d</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5db3e8ec7e08e1e1</t>
+          <t>https://www.indeed.com/viewjob?jk=555e2360433f2c3d</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04ae245d423f4f15</t>
+          <t>https://www.indeed.com/viewjob?jk=f40885146dec8a4b</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=400f98db4bb6f73d</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5035a08ea5f1e7</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555e2360433f2c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=6606e12c9ff1b3b4</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40885146dec8a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=4009b2546e8fe076</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5035a08ea5f1e7</t>
+          <t>https://www.indeed.com/viewjob?jk=ac7f86149a2ec340</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6606e12c9ff1b3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=d56d5772e687db6e</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4009b2546e8fe076</t>
+          <t>https://www.indeed.com/viewjob?jk=50c3341377ed57a3</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac7f86149a2ec340</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f65756a24c765f</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56d5772e687db6e</t>
+          <t>https://www.indeed.com/viewjob?jk=666278eb7c24f496</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c3341377ed57a3</t>
+          <t>https://www.indeed.com/viewjob?jk=77709f84c9c6155a</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f65756a24c765f</t>
+          <t>https://www.indeed.com/viewjob?jk=280432393e5a110e</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=666278eb7c24f496</t>
+          <t>https://www.indeed.com/viewjob?jk=e86adf0022116a65</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77709f84c9c6155a</t>
+          <t>https://www.indeed.com/viewjob?jk=6e612de3275e3115</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=280432393e5a110e</t>
+          <t>https://www.indeed.com/viewjob?jk=677d6d574c5b3ec3</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e86adf0022116a65</t>
+          <t>https://www.indeed.com/viewjob?jk=5466c81ac58d34ff</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e612de3275e3115</t>
+          <t>https://www.indeed.com/viewjob?jk=5b330ccc7aa453c5</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677d6d574c5b3ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=a26e11c7ee167aed</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5466c81ac58d34ff</t>
+          <t>https://www.indeed.com/viewjob?jk=2ec69fe49ff8d9dd</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b330ccc7aa453c5</t>
+          <t>https://www.indeed.com/viewjob?jk=126ea7cdef071597</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a26e11c7ee167aed</t>
+          <t>https://www.indeed.com/viewjob?jk=73105a0a5b0d4d0a</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec69fe49ff8d9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=48cce4424eee2763</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126ea7cdef071597</t>
+          <t>https://www.indeed.com/viewjob?jk=eeff413ec474b08b</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73105a0a5b0d4d0a</t>
+          <t>https://www.indeed.com/viewjob?jk=8af2618770b10440</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48cce4424eee2763</t>
+          <t>https://www.indeed.com/viewjob?jk=50b3e493edc2083f</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeff413ec474b08b</t>
+          <t>https://www.indeed.com/viewjob?jk=ba3bf92b7f61bf8b</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8af2618770b10440</t>
+          <t>https://www.indeed.com/viewjob?jk=7383fef92c3e822c</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b3e493edc2083f</t>
+          <t>https://www.indeed.com/viewjob?jk=46c1031df8a5a78f</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3bf92b7f61bf8b</t>
+          <t>https://www.indeed.com/viewjob?jk=24a79838f620ae29</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7383fef92c3e822c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff04d88198df5a34</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46c1031df8a5a78f</t>
+          <t>https://www.indeed.com/viewjob?jk=801eb4fb019f4e56</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a79838f620ae29</t>
+          <t>https://www.indeed.com/viewjob?jk=1756687393957d87</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff04d88198df5a34</t>
+          <t>https://www.indeed.com/viewjob?jk=a51ae7d37b780a38</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=801eb4fb019f4e56</t>
+          <t>https://www.indeed.com/viewjob?jk=e6a6987c98089cbb</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1756687393957d87</t>
+          <t>https://www.indeed.com/viewjob?jk=0cca6c31994af17d</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a51ae7d37b780a38</t>
+          <t>https://www.indeed.com/viewjob?jk=75d7d20700151ded</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a6987c98089cbb</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6fa018886126e9</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cca6c31994af17d</t>
+          <t>https://www.indeed.com/viewjob?jk=43627fd85a12efa0</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d7d20700151ded</t>
+          <t>https://www.indeed.com/viewjob?jk=84ae12f4cb92ce29</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6fa018886126e9</t>
+          <t>https://www.indeed.com/viewjob?jk=662d5c581b3eff4c</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43627fd85a12efa0</t>
+          <t>https://www.indeed.com/viewjob?jk=51d6fa2517837adc</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ae12f4cb92ce29</t>
+          <t>https://www.indeed.com/viewjob?jk=b66be563d1df5434</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=662d5c581b3eff4c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c258712e0383042</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51d6fa2517837adc</t>
+          <t>https://www.indeed.com/viewjob?jk=dc2b6b27a7b388ce</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b66be563d1df5434</t>
+          <t>https://www.indeed.com/viewjob?jk=30f6e0934dbdb9a0</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,14 +6236,14 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c258712e0383042</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9fddf6b4dcba23</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Application Architect</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2b6b27a7b388ce</t>
+          <t>https://www.indeed.com/viewjob?jk=4b06cd6e272dc273</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Sr Python Developer - Onsite</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f6e0934dbdb9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>La Mesa RV Center</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9fddf6b4dcba23</t>
+          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Application Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,24 +6376,24 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b06cd6e272dc273</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>La Mesa RV Center</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,24 +6446,24 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Support Engineer</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
+          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,34 +6506,34 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Murmuration</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,24 +6551,24 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Senior Support Engineer</t>
+          <t>APIGEE Development Engineer</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,24 +6586,24 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
+          <t>https://www.indeed.com/viewjob?jk=fce9a26ec94275c2</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer / SDE</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Makpar Corporation</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,77 +6611,77 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=644ffd1ada2946fd</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Murmuration</t>
+          <t>Redwood Trust</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
+          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>APIGEE Development Engineer</t>
+          <t>DevOps/Platform Engineer</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6691,32 +6691,32 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce9a26ec94275c2</t>
+          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Makpar Corporation</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=644ffd1ada2946fd</t>
+          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer, Java Full Stack</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,19 +6761,19 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java Full Stack</t>
+          <t>Data Analytics Engineer II - IM Enterprise Data</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>CHRISTUS Health</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6786,34 +6786,34 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer II - IM Enterprise Data</t>
+          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>CHRISTUS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,34 +6821,34 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
+          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Python Full Stack Developer Associate Software Engineer</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Redwood Trust</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,34 +6856,34 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
+          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>DevOps/Platform Engineer</t>
+          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6901,24 +6901,24 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
+          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6936,24 +6936,24 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
+          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Java Python Full Stack Developer Associate Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6971,24 +6971,24 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
+          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
+          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>IonQ</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7006,24 +7006,24 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
+          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Curana Health</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,34 +7031,34 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Teza Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,34 +7066,34 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
+          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>IonQ</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -7111,24 +7111,24 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
+          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Data Architect - Data Lake &amp; Data Engineering</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -7145,146 +7145,6 @@
         </is>
       </c>
       <c r="G192" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2dd3db330a009de</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Curana Health</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>AI Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Doral, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>ICF</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>ICF</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c2b1378a08eea421</t>
         </is>

--- a/results/job_matches_2026-03-21.xlsx
+++ b/results/job_matches_2026-03-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G192"/>
+  <dimension ref="A1:G191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1204728c106ec46</t>
+          <t>https://www.indeed.com/viewjob?jk=1fecb0cbc521360f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fecb0cbc521360f</t>
+          <t>https://www.indeed.com/viewjob?jk=d1204728c106ec46</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Solutions Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hadoop, Spark, PySpark, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e5351d1c126599</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
+          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer-60009025</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>State of South Carolina</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
+          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer II</t>
+          <t>Data Engineer-60009025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>State of South Carolina</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hadoop, Spark, PySpark, Snowflake, Oracle</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e5351d1c126599</t>
+          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer III (SWES03) DT_AI/ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CNC Software</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III (SWES03) DT_AI/ML</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CNC Software</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
+          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
         </is>
       </c>
     </row>
@@ -1273,52 +1273,52 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>System Architect – Database Focus</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>Independence Pet Holdings</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Walpole, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3463b2ed33bb410</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a6d5ce748599c6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II_AI/ML</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Independence Pet Holdings</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a6d5ce748599c6</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f638e48249099e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer II_AI/ML</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Coastal Credit Union</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f638e48249099e</t>
+          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Coastal Credit Union</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
+          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
+          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
         </is>
       </c>
     </row>
@@ -1483,25 +1483,25 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>Software Engineers</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Roseland, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,69 +1571,69 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, RDS, Scala, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
+          <t>https://www.indeed.com/viewjob?jk=bb04b36537a2b802</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineers</t>
+          <t>Data Engineer-Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Roseland, NJ, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb04b36537a2b802</t>
+          <t>https://www.indeed.com/viewjob?jk=177880cf8dc57acd</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer-Data Platform &amp; Analytics</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177880cf8dc57acd</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Sr Software Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
+          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Software Developer</t>
+          <t>Part-Time Data Ingest Engineer (contractor)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Digital Public Library of America</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
+          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Part-Time Data Ingest Engineer (contractor)</t>
+          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Digital Public Library of America</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Harvestaff</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Harvestaff</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
+          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Snap Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
+          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
+          <t>QA Testing Analyst - Senior</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Snap Inc.</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
+          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>QA Testing Analyst - Senior</t>
+          <t>AI Engineer Senior</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
+          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cybersecurity Data Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
+          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DevCo Management</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Cybersecurity Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DevCo Management</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
+          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
+          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
+          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
+          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
+          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
+          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
+          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
+          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
+          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
+          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
+          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
+          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
+          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
+          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
+          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
+          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
+          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
+          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
+          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
+          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
+          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
+          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
+          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
+          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
+          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
+          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
+          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
+          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
+          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
+          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
+          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
+          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AWS Solution Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, Zookeeper, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ebb6287ea5ed18b</t>
+          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
+          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AI Engineer Senior</t>
+          <t>AWS Solution Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, Zookeeper, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
+          <t>https://www.indeed.com/viewjob?jk=9ebb6287ea5ed18b</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
+          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,17 +4196,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
+          <t>https://www.indeed.com/viewjob?jk=5bda9e48f1024e1e</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bda9e48f1024e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd1e9c1ff303313</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd1e9c1ff303313</t>
+          <t>https://www.indeed.com/viewjob?jk=572dd86ccc7be082</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572dd86ccc7be082</t>
+          <t>https://www.indeed.com/viewjob?jk=c071e49659e50353</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c071e49659e50353</t>
+          <t>https://www.indeed.com/viewjob?jk=56d3332bdc3b7e53</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d3332bdc3b7e53</t>
+          <t>https://www.indeed.com/viewjob?jk=9127aed6ba1f03c6</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9127aed6ba1f03c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d981d1c9de85b5</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d981d1c9de85b5</t>
+          <t>https://www.indeed.com/viewjob?jk=20ecba012dcb872c</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ecba012dcb872c</t>
+          <t>https://www.indeed.com/viewjob?jk=c50789f60821a3d7</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50789f60821a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=5db3e8ec7e08e1e1</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5db3e8ec7e08e1e1</t>
+          <t>https://www.indeed.com/viewjob?jk=04ae245d423f4f15</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04ae245d423f4f15</t>
+          <t>https://www.indeed.com/viewjob?jk=400f98db4bb6f73d</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=400f98db4bb6f73d</t>
+          <t>https://www.indeed.com/viewjob?jk=555e2360433f2c3d</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555e2360433f2c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=f40885146dec8a4b</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40885146dec8a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5035a08ea5f1e7</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5035a08ea5f1e7</t>
+          <t>https://www.indeed.com/viewjob?jk=6606e12c9ff1b3b4</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6606e12c9ff1b3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=4009b2546e8fe076</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4009b2546e8fe076</t>
+          <t>https://www.indeed.com/viewjob?jk=ac7f86149a2ec340</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac7f86149a2ec340</t>
+          <t>https://www.indeed.com/viewjob?jk=d56d5772e687db6e</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56d5772e687db6e</t>
+          <t>https://www.indeed.com/viewjob?jk=50c3341377ed57a3</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c3341377ed57a3</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f65756a24c765f</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f65756a24c765f</t>
+          <t>https://www.indeed.com/viewjob?jk=666278eb7c24f496</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=666278eb7c24f496</t>
+          <t>https://www.indeed.com/viewjob?jk=77709f84c9c6155a</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77709f84c9c6155a</t>
+          <t>https://www.indeed.com/viewjob?jk=280432393e5a110e</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=280432393e5a110e</t>
+          <t>https://www.indeed.com/viewjob?jk=e86adf0022116a65</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e86adf0022116a65</t>
+          <t>https://www.indeed.com/viewjob?jk=6e612de3275e3115</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e612de3275e3115</t>
+          <t>https://www.indeed.com/viewjob?jk=677d6d574c5b3ec3</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677d6d574c5b3ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=5466c81ac58d34ff</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5466c81ac58d34ff</t>
+          <t>https://www.indeed.com/viewjob?jk=5b330ccc7aa453c5</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b330ccc7aa453c5</t>
+          <t>https://www.indeed.com/viewjob?jk=a26e11c7ee167aed</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a26e11c7ee167aed</t>
+          <t>https://www.indeed.com/viewjob?jk=2ec69fe49ff8d9dd</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec69fe49ff8d9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=126ea7cdef071597</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126ea7cdef071597</t>
+          <t>https://www.indeed.com/viewjob?jk=73105a0a5b0d4d0a</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73105a0a5b0d4d0a</t>
+          <t>https://www.indeed.com/viewjob?jk=48cce4424eee2763</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48cce4424eee2763</t>
+          <t>https://www.indeed.com/viewjob?jk=eeff413ec474b08b</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeff413ec474b08b</t>
+          <t>https://www.indeed.com/viewjob?jk=8af2618770b10440</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8af2618770b10440</t>
+          <t>https://www.indeed.com/viewjob?jk=50b3e493edc2083f</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b3e493edc2083f</t>
+          <t>https://www.indeed.com/viewjob?jk=ba3bf92b7f61bf8b</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3bf92b7f61bf8b</t>
+          <t>https://www.indeed.com/viewjob?jk=7383fef92c3e822c</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7383fef92c3e822c</t>
+          <t>https://www.indeed.com/viewjob?jk=46c1031df8a5a78f</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46c1031df8a5a78f</t>
+          <t>https://www.indeed.com/viewjob?jk=24a79838f620ae29</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a79838f620ae29</t>
+          <t>https://www.indeed.com/viewjob?jk=ff04d88198df5a34</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff04d88198df5a34</t>
+          <t>https://www.indeed.com/viewjob?jk=801eb4fb019f4e56</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=801eb4fb019f4e56</t>
+          <t>https://www.indeed.com/viewjob?jk=1756687393957d87</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1756687393957d87</t>
+          <t>https://www.indeed.com/viewjob?jk=a51ae7d37b780a38</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a51ae7d37b780a38</t>
+          <t>https://www.indeed.com/viewjob?jk=e6a6987c98089cbb</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a6987c98089cbb</t>
+          <t>https://www.indeed.com/viewjob?jk=0cca6c31994af17d</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cca6c31994af17d</t>
+          <t>https://www.indeed.com/viewjob?jk=75d7d20700151ded</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d7d20700151ded</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6fa018886126e9</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6fa018886126e9</t>
+          <t>https://www.indeed.com/viewjob?jk=43627fd85a12efa0</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43627fd85a12efa0</t>
+          <t>https://www.indeed.com/viewjob?jk=84ae12f4cb92ce29</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ae12f4cb92ce29</t>
+          <t>https://www.indeed.com/viewjob?jk=662d5c581b3eff4c</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=662d5c581b3eff4c</t>
+          <t>https://www.indeed.com/viewjob?jk=51d6fa2517837adc</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51d6fa2517837adc</t>
+          <t>https://www.indeed.com/viewjob?jk=b66be563d1df5434</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b66be563d1df5434</t>
+          <t>https://www.indeed.com/viewjob?jk=4c258712e0383042</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c258712e0383042</t>
+          <t>https://www.indeed.com/viewjob?jk=dc2b6b27a7b388ce</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2b6b27a7b388ce</t>
+          <t>https://www.indeed.com/viewjob?jk=30f6e0934dbdb9a0</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,14 +6201,14 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f6e0934dbdb9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9fddf6b4dcba23</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Application Architect</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9fddf6b4dcba23</t>
+          <t>https://www.indeed.com/viewjob?jk=4b06cd6e272dc273</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Application Architect</t>
+          <t>Sr Python Developer - Onsite</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b06cd6e272dc273</t>
+          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>La Mesa RV Center</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>La Mesa RV Center</t>
+          <t>Murmuration</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
+          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
         </is>
       </c>
     </row>
@@ -6523,17 +6523,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>APIGEE Development Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Murmuration</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,24 +6551,24 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
+          <t>https://www.indeed.com/viewjob?jk=fce9a26ec94275c2</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>APIGEE Development Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Makpar Corporation</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,32 +6586,32 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce9a26ec94275c2</t>
+          <t>https://www.indeed.com/viewjob?jk=644ffd1ada2946fd</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Makpar Corporation</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,24 +6621,24 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=644ffd1ada2946fd</t>
+          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer, Java Full Stack</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Redwood Trust</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,34 +6646,34 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>DevOps/Platform Engineer</t>
+          <t>Data Analytics Engineer II - IM Enterprise Data</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CHRISTUS Health</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,34 +6681,34 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
+          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Redwood Trust</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,34 +6716,34 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java Full Stack</t>
+          <t>DevOps/Platform Engineer</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
+          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer II - IM Enterprise Data</t>
+          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>CHRISTUS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,24 +6786,24 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
+          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
+          <t>Java Python Full Stack Developer Associate Software Engineer</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6831,14 +6831,14 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
+          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Java Python Full Stack Developer Associate Software Engineer</t>
+          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,24 +6866,24 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
+          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Curana Health</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,34 +6891,34 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,34 +6926,34 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
+          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Teza Technologies</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6971,24 +6971,24 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
+          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>IonQ</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7006,24 +7006,24 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
+          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Curana Health</t>
+          <t>IonQ</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,34 +7031,34 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
+          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,17 +7066,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
         </is>
       </c>
     </row>
@@ -7110,41 +7110,6 @@
         </is>
       </c>
       <c r="G191" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>ICF</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c2b1378a08eea421</t>
         </is>

--- a/results/job_matches_2026-03-21.xlsx
+++ b/results/job_matches_2026-03-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G191"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
+          <t>https://www.indeed.com/viewjob?jk=0673331b89873626</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
+          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer-60009025</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>State of South Carolina</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,52 +1011,52 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
+          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Data Engineer-60009025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>State of South Carolina</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b81ca9e34e5e9f1</t>
+          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520c71629e4ae31f</t>
+          <t>https://www.indeed.com/viewjob?jk=3b81ca9e34e5e9f1</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b820a060e96568</t>
+          <t>https://www.indeed.com/viewjob?jk=520c71629e4ae31f</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce993d8d61236e3</t>
+          <t>https://www.indeed.com/viewjob?jk=96b820a060e96568</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CNC Software</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce993d8d61236e3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer III (SWES03) DT_AI/ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CNC Software</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software Engineer III (SWES03) DT_AI/ML</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cooper Standard</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northville, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,69 +1256,69 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=419f48f4c723af35</t>
+          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Independence Pet Holdings</t>
+          <t>Cooper Standard</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Northville, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a6d5ce748599c6</t>
+          <t>https://www.indeed.com/viewjob?jk=419f48f4c723af35</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer II_AI/ML</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Independence Pet Holdings</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f638e48249099e</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a6d5ce748599c6</t>
         </is>
       </c>
     </row>
@@ -1553,52 +1553,52 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineers</t>
+          <t>Data Engineer-Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Roseland, NJ, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb04b36537a2b802</t>
+          <t>https://www.indeed.com/viewjob?jk=177880cf8dc57acd</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer-Data Platform &amp; Analytics</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177880cf8dc57acd</t>
+          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Part-Time Data Ingest Engineer (contractor)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Digital Public Library of America</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
+          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Software Developer</t>
+          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Part-Time Data Ingest Engineer (contractor)</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Digital Public Library of America</t>
+          <t>Harvestaff</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
+          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Sr Software Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Harvestaff</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
+          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Snap Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
+          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
+          <t>QA Testing Analyst - Senior</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Snap Inc.</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
+          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>QA Testing Analyst - Senior</t>
+          <t>AI Engineer Senior</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
+          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Engineer Senior</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
+          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
         </is>
       </c>
     </row>
@@ -1961,29 +1961,29 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Cybersecurity Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cybersecurity Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DevCo Management</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
+          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DevCo Management</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
+          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
+          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
+          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
+          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
+          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
+          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
+          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
+          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
+          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
+          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
+          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
+          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
+          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
+          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
+          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
+          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
+          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
+          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
+          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
+          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
+          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
+          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
+          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
+          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
+          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
+          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
+          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
+          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
+          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
+          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
+          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
+          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
+          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>AWS Solution Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, Zookeeper, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
+          <t>https://www.indeed.com/viewjob?jk=9ebb6287ea5ed18b</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AWS Solution Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, Zookeeper, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ebb6287ea5ed18b</t>
+          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Sr Python Developer - Onsite</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
+          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>La Mesa RV Center</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bda9e48f1024e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd1e9c1ff303313</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572dd86ccc7be082</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c071e49659e50353</t>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Senior Support Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d3332bdc3b7e53</t>
+          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9127aed6ba1f03c6</t>
+          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Murmuration</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d981d1c9de85b5</t>
+          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ecba012dcb872c</t>
+          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Sr. Software Engineer, Java Full Stack</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,102 +4486,102 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50789f60821a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Data Analytics Engineer II - IM Enterprise Data</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CHRISTUS Health</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5db3e8ec7e08e1e1</t>
+          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Redwood Trust</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04ae245d423f4f15</t>
+          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>DevOps/Platform Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,102 +4591,102 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=400f98db4bb6f73d</t>
+          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Curana Health</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555e2360433f2c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40885146dec8a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5035a08ea5f1e7</t>
+          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Java Python Full Stack Developer Associate Software Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6606e12c9ff1b3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4009b2546e8fe076</t>
+          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac7f86149a2ec340</t>
+          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56d5772e687db6e</t>
+          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IonQ</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c3341377ed57a3</t>
+          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f65756a24c765f</t>
+          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4940,2176 +4940,6 @@
         </is>
       </c>
       <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=666278eb7c24f496</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=77709f84c9c6155a</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=280432393e5a110e</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e86adf0022116a65</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Memphis, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e612de3275e3115</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=677d6d574c5b3ec3</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5466c81ac58d34ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b330ccc7aa453c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a26e11c7ee167aed</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec69fe49ff8d9dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Davenport, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=126ea7cdef071597</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73105a0a5b0d4d0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48cce4424eee2763</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eeff413ec474b08b</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Midland, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8af2618770b10440</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50b3e493edc2083f</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3bf92b7f61bf8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7383fef92c3e822c</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Princeton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=46c1031df8a5a78f</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24a79838f620ae29</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff04d88198df5a34</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=801eb4fb019f4e56</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1756687393957d87</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a51ae7d37b780a38</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a6987c98089cbb</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0cca6c31994af17d</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=75d7d20700151ded</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6fa018886126e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=43627fd85a12efa0</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84ae12f4cb92ce29</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Fresno, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=662d5c581b3eff4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=51d6fa2517837adc</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b66be563d1df5434</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c258712e0383042</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2b6b27a7b388ce</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30f6e0934dbdb9a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Huntsville, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9fddf6b4dcba23</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Application Architect</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b06cd6e272dc273</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Sr Python Developer - Onsite</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>M-TECH SYSTEMS</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Dunwoody, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Solution Architect</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>La Mesa RV Center</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Senior QA Engineer</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Murmuration</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>HealthMark Group</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Senior Support Engineer</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Lyric</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Senior Data Platform Engineer / SDE</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Cambia Health Solutions</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>APIGEE Development Engineer</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Morris Plains, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fce9a26ec94275c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Makpar Corporation</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CloudFormation, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=644ffd1ada2946fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>BAE Systems USA</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Rockville, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer, Java Full Stack</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Caterpillar</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Data Analytics Engineer II - IM Enterprise Data</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>CHRISTUS Health</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Redwood Trust</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>DevOps/Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Java Python Full Stack Developer Associate Software Engineer</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Curana Health</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>AI Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Doral, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Teza Technologies</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>IonQ</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Bothell, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>ICF</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>ICF</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c2b1378a08eea421</t>
         </is>

--- a/results/job_matches_2026-03-21.xlsx
+++ b/results/job_matches_2026-03-21.xlsx
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MidAmerican Energy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e463fc88ac4ddcb3</t>
+          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,42 +1441,42 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
+          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>SENIOR PRODUCT ENGINEER (HYBRID CHICAGO)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
+          <t>https://www.indeed.com/viewjob?jk=db7fd563fd960a2d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-21.xlsx
+++ b/results/job_matches_2026-03-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Part-Time Data Ingest Engineer (contractor)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Digital Public Library of America</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3bab5f2ccae161</t>
+          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Part-Time Data Ingest Engineer (contractor)</t>
+          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Digital Public Library of America</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Harvestaff</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Harvestaff</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
+          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Sr Software Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
+          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Software Developer</t>
+          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Snap Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
+          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
+          <t>QA Testing Analyst - Senior</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Snap Inc.</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
+          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>QA Testing Analyst - Senior</t>
+          <t>AI Engineer Senior</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
+          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Engineer Senior</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
+          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
         </is>
       </c>
     </row>
@@ -1926,29 +1926,29 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Cybersecurity Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cybersecurity Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DevCo Management</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
+          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DevCo Management</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
+          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
+          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
+          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
+          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
+          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
+          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
+          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
+          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
+          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
+          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
+          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
+          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
+          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
+          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
+          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
+          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
+          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
+          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
+          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
+          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
+          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
+          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
+          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
+          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
+          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
+          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
+          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
+          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
+          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
+          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
+          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
+          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
+          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>AWS Solution Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, Zookeeper, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
+          <t>https://www.indeed.com/viewjob?jk=9ebb6287ea5ed18b</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AWS Solution Engineer</t>
+          <t>Sr Python Developer - Onsite</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, Zookeeper, Scala, Kafka, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ebb6287ea5ed18b</t>
+          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>La Mesa RV Center</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, SQS, SNS, API Gateway, RDS, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf20edf4b871568c</t>
+          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>La Mesa RV Center</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Support Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Support Engineer</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Murmuration</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,67 +4346,67 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
+          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer / SDE</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>Sr. Software Engineer, Java Full Stack</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Murmuration</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics Engineer II - IM Enterprise Data</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>CHRISTUS Health</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java Full Stack</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Redwood Trust</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
+          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer II - IM Enterprise Data</t>
+          <t>DevOps/Platform Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CHRISTUS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
+          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Redwood Trust</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
+          <t>https://www.indeed.com/viewjob?jk=a12794620257c6fd</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DevOps/Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Curana Health</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Curana Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
+          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer</t>
+          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,24 +4651,24 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
+          <t>Java Python Full Stack Developer Associate Software Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4696,14 +4696,14 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
+          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Java Python Full Stack Developer Associate Software Engineer</t>
+          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
+          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
+          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
+          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Teza Technologies</t>
+          <t>IonQ</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
+          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>IonQ</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
+          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
         </is>
       </c>
     </row>
@@ -4905,41 +4905,6 @@
         </is>
       </c>
       <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>ICF</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c2b1378a08eea421</t>
         </is>

--- a/results/job_matches_2026-03-21.xlsx
+++ b/results/job_matches_2026-03-21.xlsx
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fecb0cbc521360f</t>
+          <t>https://www.indeed.com/viewjob?jk=d1204728c106ec46</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1204728c106ec46</t>
+          <t>https://www.indeed.com/viewjob?jk=1fecb0cbc521360f</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer II</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hadoop, Spark, PySpark, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e5351d1c126599</t>
+          <t>https://www.indeed.com/viewjob?jk=0673331b89873626</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0673331b89873626</t>
+          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
+          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Data Solutions Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hadoop, Spark, PySpark, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,42 +1021,42 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e5351d1c126599</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer-60009025</t>
+          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>State of South Carolina</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730fc0393aed5ee7</t>
+          <t>https://www.indeed.com/viewjob?jk=3b81ca9e34e5e9f1</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b81ca9e34e5e9f1</t>
+          <t>https://www.indeed.com/viewjob?jk=520c71629e4ae31f</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520c71629e4ae31f</t>
+          <t>https://www.indeed.com/viewjob?jk=96b820a060e96568</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b820a060e96568</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce993d8d61236e3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Software Engineer III (SWES03) DT_AI/ML</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce993d8d61236e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer III (SWES03) DT_AI/ML</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cooper Standard</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Northville, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,69 +1256,69 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=419f48f4c723af35</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cooper Standard</t>
+          <t>Independence Pet Holdings</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Northville, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=419f48f4c723af35</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a6d5ce748599c6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Independence Pet Holdings</t>
+          <t>Coastal Credit Union</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a6d5ce748599c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Coastal Credit Union</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
+          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
         </is>
       </c>
     </row>
@@ -1413,42 +1413,42 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>SENIOR PRODUCT ENGINEER (HYBRID CHICAGO)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
+          <t>https://www.indeed.com/viewjob?jk=db7fd563fd960a2d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ENGINEER (HYBRID CHICAGO)</t>
+          <t>SENIOR PRODUCT ENGINEER (REMOTE OPPORTUNITY)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1471,29 +1471,29 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db7fd563fd960a2d</t>
+          <t>https://www.indeed.com/viewjob?jk=2bed15d2d90e0d1d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Cambium Learning Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
+          <t>https://www.indeed.com/viewjob?jk=c674b29c5cebe1e7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ENGINEER (REMOTE OPPORTUNITY)</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bed15d2d90e0d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Engineer Senior</t>
+          <t>Cybersecurity Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>DevCo Management</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
+          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
+          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cybersecurity Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
+          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DevCo Management</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
+          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
+          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
+          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
+          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
+          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
+          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
+          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
+          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
+          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
+          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
+          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
+          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
+          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
+          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
+          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
+          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
+          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
+          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
+          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
+          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
+          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
+          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
+          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
+          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
+          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
+          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
+          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
+          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
+          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
+          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
+          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
+          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>AWS Solution Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, Zookeeper, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
+          <t>https://www.indeed.com/viewjob?jk=9ebb6287ea5ed18b</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>AI Engineer Senior</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
+          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AWS Solution Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,17 +4056,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, Zookeeper, Scala, Kafka, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ebb6287ea5ed18b</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
         </is>
       </c>
     </row>
@@ -4108,17 +4108,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>La Mesa RV Center</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>La Mesa RV Center</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
         </is>
       </c>
     </row>
@@ -4353,17 +4353,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Redwood Trust</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java Full Stack</t>
+          <t>DevOps/Platform Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
+          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer II - IM Enterprise Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CHRISTUS Health</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
+          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
+          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer, Java Full Stack</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Redwood Trust</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DevOps/Platform Engineer</t>
+          <t>Data Analytics Engineer II - IM Enterprise Data</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CHRISTUS Health</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
+          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
         </is>
       </c>
     </row>
@@ -4563,17 +4563,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Curana Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
+          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer</t>
+          <t>Java Python Full Stack Developer Associate Software Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,24 +4616,24 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
+          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
+          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Java Python Full Stack Developer Associate Software Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
+          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
+          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>IonQ</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
+          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Teza Technologies</t>
+          <t>Curana Health</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
+          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
+          <t>AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>IonQ</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,17 +4826,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
+          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-21.xlsx
+++ b/results/job_matches_2026-03-21.xlsx
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1204728c106ec46</t>
+          <t>https://www.indeed.com/viewjob?jk=1fecb0cbc521360f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fecb0cbc521360f</t>
+          <t>https://www.indeed.com/viewjob?jk=d1204728c106ec46</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Data Solutions Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hadoop, Spark, PySpark, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0673331b89873626</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e5351d1c126599</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
+          <t>https://www.indeed.com/viewjob?jk=0673331b89873626</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
+          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer II</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hadoop, Spark, PySpark, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e5351d1c126599</t>
+          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer III (SWES03) DT_AI/ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CNC Software</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III (SWES03) DT_AI/ML</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CNC Software</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
+          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
+          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
+          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ENGINEER (REMOTE OPPORTUNITY)</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Cambium Learning Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bed15d2d90e0d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=c674b29c5cebe1e7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cambium Learning Group</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c674b29c5cebe1e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>SENIOR PRODUCT ENGINEER (REMOTE OPPORTUNITY)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
+          <t>https://www.indeed.com/viewjob?jk=2bed15d2d90e0d1d</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Part-Time Data Ingest Engineer (contractor)</t>
+          <t>Solutions Developer for the Office of HPD TECH</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Digital Public Library of America</t>
+          <t>New York City Department of Housing Preservation &amp; Development</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>S3, RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
+          <t>https://www.indeed.com/viewjob?jk=4ab98ea9cc28ff7b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
+          <t>Part-Time Data Ingest Engineer (contractor)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Digital Public Library of America</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
+          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Harvestaff</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Harvestaff</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Software Developer</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
+          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
+          <t>Sr Software Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Snap Inc.</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
+          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QA Testing Analyst - Senior</t>
+          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Snap Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,59 +1826,59 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
+          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cybersecurity Data Engineer</t>
+          <t>QA Testing Analyst - Senior</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
+          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer Senior</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DevCo Management</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
+          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Cybersecurity Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DevCo Management</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
+          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
+          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
+          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
+          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
+          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
+          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
+          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
+          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
+          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
+          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
+          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
+          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
+          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
+          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
+          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
+          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
+          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
+          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
+          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
+          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
+          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
+          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
+          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
+          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
+          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
+          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
+          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
+          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
+          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
+          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
+          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
+          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AWS Solution Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, Zookeeper, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ebb6287ea5ed18b</t>
+          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AI Engineer Senior</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
+          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
+          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
+          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite</t>
+          <t>AWS Solution Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Kinesis, IAM, Azure, Event Hubs, Zookeeper, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=9ebb6287ea5ed18b</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Python Developer - Onsite</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
+          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>La Mesa RV Center</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>La Mesa RV Center</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Support Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer / SDE</t>
+          <t>Senior Support Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Murmuration</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,69 +4336,69 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
+          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Redwood Trust</t>
+          <t>Murmuration</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
+          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DevOps/Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
+          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer, Java Full Stack</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,19 +4451,19 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java Full Stack</t>
+          <t>Data Analytics Engineer II - IM Enterprise Data</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>CHRISTUS Health</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer II - IM Enterprise Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CHRISTUS Health</t>
+          <t>Redwood Trust</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
+          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps/Platform Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>St. David's HealthCare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12794620257c6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
+          <t>https://www.indeed.com/viewjob?jk=a12794620257c6fd</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Java Python Full Stack Developer Associate Software Engineer</t>
+          <t>AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,24 +4616,24 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
+          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
+          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
+          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Java Python Full Stack Developer Associate Software Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
+          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Teza Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
+          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>IonQ</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
+          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Curana Health</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b2c9907ac74f3bf</t>
+          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer</t>
+          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>IonQ</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,17 +4826,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-21.xlsx
+++ b/results/job_matches_2026-03-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,52 +538,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – CDO / Data &amp; AI Engineering</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Spark Streaming, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c03da34050d1fb85</t>
+          <t>https://www.indeed.com/viewjob?jk=1fecb0cbc521360f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,112 +591,112 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fecb0cbc521360f</t>
+          <t>https://www.indeed.com/viewjob?jk=d1204728c106ec46</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
+          <t>Python and PySpark, No SQL Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1204728c106ec46</t>
+          <t>https://www.indeed.com/viewjob?jk=d64ff1548d48cfe8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d64ff1548d48cfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2163f01dd05b34</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Kubernetes Engineer</t>
+          <t>Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Northcross Group</t>
+          <t>Openly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Marquette, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f734c7c5315c58</t>
+          <t>https://www.indeed.com/viewjob?jk=4d18e2b948851633</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS Kubernetes Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Northcross Group</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b0cc109a6bef88b</t>
+          <t>https://www.indeed.com/viewjob?jk=e13bcfee6252358d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Solutions Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hadoop, Spark, PySpark, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2163f01dd05b34</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e5351d1c126599</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote, US)</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d18e2b948851633</t>
+          <t>https://www.indeed.com/viewjob?jk=0673331b89873626</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e13bcfee6252358d</t>
+          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer II</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hadoop, Spark, PySpark, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e5351d1c126599</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0673331b89873626</t>
+          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
+          <t>https://www.indeed.com/viewjob?jk=3b81ca9e34e5e9f1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
+          <t>https://www.indeed.com/viewjob?jk=520c71629e4ae31f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
+          <t>https://www.indeed.com/viewjob?jk=96b820a060e96568</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b81ca9e34e5e9f1</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce993d8d61236e3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CNC Software</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520c71629e4ae31f</t>
+          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Software Engineer III (SWES03) DT_AI/ML</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b820a060e96568</t>
+          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Cooper Standard</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Northville, MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce993d8d61236e3</t>
+          <t>https://www.indeed.com/viewjob?jk=419f48f4c723af35</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CNC Software</t>
+          <t>Independence Pet Holdings</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a6d5ce748599c6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer III (SWES03) DT_AI/ML</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Coastal Credit Union</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,59 +1231,59 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cooper Standard</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northville, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=419f48f4c723af35</t>
+          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Independence Pet Holdings</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a6d5ce748599c6</t>
+          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>SENIOR PRODUCT ENGINEER (HYBRID CHICAGO)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Coastal Credit Union</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
+          <t>https://www.indeed.com/viewjob?jk=db7fd563fd960a2d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cambium Learning Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
+          <t>https://www.indeed.com/viewjob?jk=c674b29c5cebe1e7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ENGINEER (HYBRID CHICAGO)</t>
+          <t>SENIOR PRODUCT ENGINEER (REMOTE OPPORTUNITY)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1436,29 +1436,29 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db7fd563fd960a2d</t>
+          <t>https://www.indeed.com/viewjob?jk=2bed15d2d90e0d1d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Software Engineers</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cambium Learning Group</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Roseland, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Scala, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c674b29c5cebe1e7</t>
+          <t>https://www.indeed.com/viewjob?jk=bb04b36537a2b802</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>Data Engineer-Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,59 +1511,59 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
+          <t>https://www.indeed.com/viewjob?jk=177880cf8dc57acd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ENGINEER (REMOTE OPPORTUNITY)</t>
+          <t>Solutions Developer for the Office of HPD TECH</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>New York City Department of Housing Preservation &amp; Development</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
+          <t>S3, RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bed15d2d90e0d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=4ab98ea9cc28ff7b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer-Data Platform &amp; Analytics</t>
+          <t>Part-Time Data Ingest Engineer (contractor)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Digital Public Library of America</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177880cf8dc57acd</t>
+          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Solutions Developer for the Office of HPD TECH</t>
+          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>New York City Department of Housing Preservation &amp; Development</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ab98ea9cc28ff7b</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Part-Time Data Ingest Engineer (contractor)</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Digital Public Library of America</t>
+          <t>Harvestaff</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
+          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Sr Software Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Harvestaff</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
+          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Snap Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
+          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Software Developer</t>
+          <t>QA Testing Analyst - Senior</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
+          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
+          <t>AI Engineer Senior</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Snap Inc.</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
+          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>QA Testing Analyst - Senior</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
+          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Engineer Senior</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Cybersecurity Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>DevCo Management</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
+          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cybersecurity Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
+          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DevCo Management</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
+          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
+          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
+          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
+          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
+          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
+          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
+          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
+          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
+          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
+          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
+          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
+          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
+          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
+          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
+          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
+          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
+          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
+          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
+          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
+          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
+          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
+          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
+          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
+          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
+          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
+          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
+          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
+          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
+          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
+          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
+          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
+          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
+          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,14 +3996,14 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
+          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,14 +4031,14 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=5bda9e48f1024e1e</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd1e9c1ff303313</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AWS Solution Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Event Hubs, Zookeeper, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ebb6287ea5ed18b</t>
+          <t>https://www.indeed.com/viewjob?jk=572dd86ccc7be082</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=c071e49659e50353</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>La Mesa RV Center</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
+          <t>https://www.indeed.com/viewjob?jk=56d3332bdc3b7e53</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
+          <t>https://www.indeed.com/viewjob?jk=9127aed6ba1f03c6</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d981d1c9de85b5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=20ecba012dcb872c</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Support Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
+          <t>https://www.indeed.com/viewjob?jk=c50789f60821a3d7</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer / SDE</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=5db3e8ec7e08e1e1</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Murmuration</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
+          <t>https://www.indeed.com/viewjob?jk=04ae245d423f4f15</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=400f98db4bb6f73d</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java Full Stack</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,102 +4451,102 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
+          <t>https://www.indeed.com/viewjob?jk=555e2360433f2c3d</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer II - IM Enterprise Data</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CHRISTUS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
+          <t>https://www.indeed.com/viewjob?jk=f40885146dec8a4b</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Redwood Trust</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
+          <t>https://www.indeed.com/viewjob?jk=8d5035a08ea5f1e7</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DevOps/Platform Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,102 +4556,102 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
+          <t>https://www.indeed.com/viewjob?jk=6606e12c9ff1b3b4</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>St. David's HealthCare</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12794620257c6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=4009b2546e8fe076</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=ac7f86149a2ec340</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
+          <t>https://www.indeed.com/viewjob?jk=d56d5772e687db6e</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Java Python Full Stack Developer Associate Software Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
+          <t>https://www.indeed.com/viewjob?jk=50c3341377ed57a3</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f65756a24c765f</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
+          <t>https://www.indeed.com/viewjob?jk=666278eb7c24f496</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Teza Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
+          <t>https://www.indeed.com/viewjob?jk=77709f84c9c6155a</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>IonQ</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
+          <t>https://www.indeed.com/viewjob?jk=280432393e5a110e</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,40 +4871,2070 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
+          <t>https://www.indeed.com/viewjob?jk=e86adf0022116a65</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e612de3275e3115</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=677d6d574c5b3ec3</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5466c81ac58d34ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b330ccc7aa453c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a26e11c7ee167aed</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ec69fe49ff8d9dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=126ea7cdef071597</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73105a0a5b0d4d0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48cce4424eee2763</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eeff413ec474b08b</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Midland, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8af2618770b10440</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50b3e493edc2083f</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba3bf92b7f61bf8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7383fef92c3e822c</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46c1031df8a5a78f</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24a79838f620ae29</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff04d88198df5a34</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=801eb4fb019f4e56</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1756687393957d87</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a51ae7d37b780a38</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6a6987c98089cbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0cca6c31994af17d</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75d7d20700151ded</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c6fa018886126e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43627fd85a12efa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84ae12f4cb92ce29</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Fresno, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=662d5c581b3eff4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51d6fa2517837adc</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b66be563d1df5434</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c258712e0383042</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc2b6b27a7b388ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30f6e0934dbdb9a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b9fddf6b4dcba23</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Application Architect</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b06cd6e272dc273</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Sr Python Developer - Onsite</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>M-TECH SYSTEMS</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Dunwoody, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Solution Architect</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>La Mesa RV Center</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>HealthMark Group</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Senior Support Engineer</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Lyric</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Senior Data Platform Engineer / SDE</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Cambia Health Solutions</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Senior QA Engineer</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Murmuration</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>APIGEE Development Engineer</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Morris Plains, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fce9a26ec94275c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Makpar Corporation</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CloudFormation, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=644ffd1ada2946fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>BAE Systems USA</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Rockville, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer, Java Full Stack</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Data Analytics Engineer II - IM Enterprise Data</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>CHRISTUS Health</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Redwood Trust</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>DevOps/Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>St. David's HealthCare</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a12794620257c6fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>AI Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Doral, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Java Python Full Stack Developer Associate Software Engineer</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Teza Technologies</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>IonQ</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Bothell, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
           <t>Business Intelligence Developer</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B185" t="inlineStr">
         <is>
           <t>ICF</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C185" t="inlineStr">
         <is>
           <t>Reston, VA, US USA</t>
         </is>
       </c>
-      <c r="D128" t="n">
+      <c r="D185" t="n">
         <v>10.4</v>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="E185" t="inlineStr">
         <is>
           <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>ICF</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c2b1378a08eea421</t>
         </is>

--- a/results/job_matches_2026-03-21.xlsx
+++ b/results/job_matches_2026-03-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G186"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,130 +573,130 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Junior AI/ML Engineer (Data &amp; Cloud Platforms)</t>
+          <t>Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>Openly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1204728c106ec46</t>
+          <t>https://www.indeed.com/viewjob?jk=4d18e2b948851633</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer</t>
+          <t>Software Engineer Sr - Check Modernization and Adjustment Team</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d64ff1548d48cfe8</t>
+          <t>https://www.indeed.com/viewjob?jk=b695d5219c5f3d42</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2163f01dd05b34</t>
+          <t>https://www.indeed.com/viewjob?jk=e13bcfee6252358d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote, US)</t>
+          <t>Data Solutions Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hadoop, Spark, PySpark, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d18e2b948851633</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e5351d1c126599</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e13bcfee6252358d</t>
+          <t>https://www.indeed.com/viewjob?jk=0673331b89873626</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer II</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hadoop, Spark, PySpark, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e5351d1c126599</t>
+          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0673331b89873626</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
+          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
+          <t>https://www.indeed.com/viewjob?jk=3b81ca9e34e5e9f1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
+          <t>https://www.indeed.com/viewjob?jk=520c71629e4ae31f</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b81ca9e34e5e9f1</t>
+          <t>https://www.indeed.com/viewjob?jk=96b820a060e96568</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520c71629e4ae31f</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce993d8d61236e3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Software Engineer III (SWES03) DT_AI/ML</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b820a060e96568</t>
+          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Cooper Standard</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Northville, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce993d8d61236e3</t>
+          <t>https://www.indeed.com/viewjob?jk=419f48f4c723af35</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CNC Software</t>
+          <t>Independence Pet Holdings</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ead6759ac7d0a47</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a6d5ce748599c6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III (SWES03) DT_AI/ML</t>
+          <t>Data Engineer Sr</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Coastal Credit Union</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cooper Standard</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northville, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=419f48f4c723af35</t>
+          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Independence Pet Holdings</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a6d5ce748599c6</t>
+          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Coastal Credit Union</t>
+          <t>Cambium Learning Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
+          <t>https://www.indeed.com/viewjob?jk=c674b29c5cebe1e7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Sales Engineer, Commercial Expansion</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fivetran</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,49 +1266,49 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>SENIOR PRODUCT ENGINEER (HYBRID CHICAGO)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
+          <t>https://www.indeed.com/viewjob?jk=db7fd563fd960a2d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ENGINEER (HYBRID CHICAGO)</t>
+          <t>SENIOR PRODUCT ENGINEER (REMOTE OPPORTUNITY)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1331,37 +1331,37 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db7fd563fd960a2d</t>
+          <t>https://www.indeed.com/viewjob?jk=2bed15d2d90e0d1d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Engineer-Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cambium Learning Group</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c674b29c5cebe1e7</t>
+          <t>https://www.indeed.com/viewjob?jk=177880cf8dc57acd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>Part-Time Data Ingest Engineer (contractor)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Digital Public Library of America</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
+          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ENGINEER (REMOTE OPPORTUNITY)</t>
+          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bed15d2d90e0d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineers</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>Harvestaff</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Roseland, NJ, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Jenkins</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb04b36537a2b802</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer-Data Platform &amp; Analytics</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177880cf8dc57acd</t>
+          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Solutions Developer for the Office of HPD TECH</t>
+          <t>Sr Software Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>New York City Department of Housing Preservation &amp; Development</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ab98ea9cc28ff7b</t>
+          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Part-Time Data Ingest Engineer (contractor)</t>
+          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Digital Public Library of America</t>
+          <t>Snap Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
+          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
+          <t>QA Testing Analyst - Senior</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
+          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>AI Engineer Senior</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Harvestaff</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
+          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,54 +1686,54 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
+          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Software Developer</t>
+          <t>Cybersecurity Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Snap Inc.</t>
+          <t>DevCo Management</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1742,11 +1742,11 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
+          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QA Testing Analyst - Senior</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
+          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Engineer Senior</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
+          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
+          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa0447b668a6f99</t>
+          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cybersecurity Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
+          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DevCo Management</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
+          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
+          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
+          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
+          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
+          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
+          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
+          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
+          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
+          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
+          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
+          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
+          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
+          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
+          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
+          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
+          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
+          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
+          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
+          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
+          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
+          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
+          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
+          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
+          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
+          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
+          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
+          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
+          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Sr Python Developer - Onsite</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
+          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>La Mesa RV Center</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Senior Support Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
+          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Murmuration</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bda9e48f1024e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd1e9c1ff303313</t>
+          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Sr. Software Engineer, Java Full Stack</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,102 +4101,102 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572dd86ccc7be082</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Data Analytics Engineer II - IM Enterprise Data</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CHRISTUS Health</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c071e49659e50353</t>
+          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Redwood Trust</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d3332bdc3b7e53</t>
+          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>DevOps/Platform Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,67 +4206,67 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9127aed6ba1f03c6</t>
+          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d981d1c9de85b5</t>
+          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ecba012dcb872c</t>
+          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Java Python Full Stack Developer Associate Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c50789f60821a3d7</t>
+          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5db3e8ec7e08e1e1</t>
+          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04ae245d423f4f15</t>
+          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=400f98db4bb6f73d</t>
+          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>IonQ</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555e2360433f2c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40885146dec8a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Senior Consultant</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4520,2421 +4520,6 @@
         </is>
       </c>
       <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5035a08ea5f1e7</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6606e12c9ff1b3b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4009b2546e8fe076</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac7f86149a2ec340</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d56d5772e687db6e</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50c3341377ed57a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f65756a24c765f</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Dayton, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=666278eb7c24f496</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=77709f84c9c6155a</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=280432393e5a110e</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e86adf0022116a65</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Memphis, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e612de3275e3115</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=677d6d574c5b3ec3</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5466c81ac58d34ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b330ccc7aa453c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a26e11c7ee167aed</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec69fe49ff8d9dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Davenport, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=126ea7cdef071597</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73105a0a5b0d4d0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48cce4424eee2763</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eeff413ec474b08b</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Midland, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8af2618770b10440</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50b3e493edc2083f</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3bf92b7f61bf8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7383fef92c3e822c</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Princeton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=46c1031df8a5a78f</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24a79838f620ae29</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff04d88198df5a34</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=801eb4fb019f4e56</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1756687393957d87</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a51ae7d37b780a38</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a6987c98089cbb</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0cca6c31994af17d</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=75d7d20700151ded</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6fa018886126e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=43627fd85a12efa0</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84ae12f4cb92ce29</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Fresno, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=662d5c581b3eff4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=51d6fa2517837adc</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b66be563d1df5434</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c258712e0383042</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2b6b27a7b388ce</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30f6e0934dbdb9a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Huntsville, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9fddf6b4dcba23</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Application Architect</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b06cd6e272dc273</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Sr Python Developer - Onsite</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>M-TECH SYSTEMS</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Dunwoody, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Solution Architect</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>La Mesa RV Center</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>HealthMark Group</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Senior Support Engineer</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Lyric</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Senior Data Platform Engineer / SDE</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Cambia Health Solutions</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Senior QA Engineer</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Murmuration</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>APIGEE Development Engineer</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Morris Plains, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fce9a26ec94275c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Makpar Corporation</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CloudFormation, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=644ffd1ada2946fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>BAE Systems USA</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Rockville, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer, Java Full Stack</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Caterpillar</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Data Analytics Engineer II - IM Enterprise Data</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>CHRISTUS Health</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Redwood Trust</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>DevOps/Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>St. David's HealthCare</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a12794620257c6fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>AI Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Doral, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Java Python Full Stack Developer Associate Software Engineer</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Teza Technologies</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>IonQ</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Bothell, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>ICF</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>ICF</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c2b1378a08eea421</t>
         </is>

--- a/results/job_matches_2026-03-21.xlsx
+++ b/results/job_matches_2026-03-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote, US)</t>
+          <t>Software Engineer Sr - Check Modernization and Adjustment Team</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d18e2b948851633</t>
+          <t>https://www.indeed.com/viewjob?jk=b695d5219c5f3d42</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer Sr - Check Modernization and Adjustment Team</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b695d5219c5f3d42</t>
+          <t>https://www.indeed.com/viewjob?jk=e13bcfee6252358d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Solutions Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hadoop, Spark, PySpark, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e13bcfee6252358d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e5351d1c126599</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer II</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hadoop, Spark, PySpark, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e5351d1c126599</t>
+          <t>https://www.indeed.com/viewjob?jk=0673331b89873626</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0673331b89873626</t>
+          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
+          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
+          <t>https://www.indeed.com/viewjob?jk=3b81ca9e34e5e9f1</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b81ca9e34e5e9f1</t>
+          <t>https://www.indeed.com/viewjob?jk=520c71629e4ae31f</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520c71629e4ae31f</t>
+          <t>https://www.indeed.com/viewjob?jk=96b820a060e96568</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b820a060e96568</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce993d8d61236e3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Software Engineer III (SWES03) DT_AI/ML</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce993d8d61236e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer III (SWES03) DT_AI/ML</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cooper Standard</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Northville, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,69 +1011,69 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=419f48f4c723af35</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cooper Standard</t>
+          <t>Independence Pet Holdings</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Northville, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=419f48f4c723af35</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a6d5ce748599c6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Independence Pet Holdings</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a6d5ce748599c6</t>
+          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer Sr</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Coastal Credit Union</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96bcd9b2b20e586</t>
+          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cambium Learning Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,59 +1161,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
+          <t>https://www.indeed.com/viewjob?jk=c674b29c5cebe1e7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>SENIOR PRODUCT ENGINEER (HYBRID CHICAGO)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
+          <t>https://www.indeed.com/viewjob?jk=db7fd563fd960a2d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>SENIOR PRODUCT ENGINEER (REMOTE OPPORTUNITY)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cambium Learning Group</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c674b29c5cebe1e7</t>
+          <t>https://www.indeed.com/viewjob?jk=2bed15d2d90e0d1d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Sales Engineer, Commercial Expansion</t>
+          <t>Data Engineer-Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fivetran</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Snowflake, Oracle, SQL Server, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a965c884f4afb0</t>
+          <t>https://www.indeed.com/viewjob?jk=177880cf8dc57acd</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ENGINEER (HYBRID CHICAGO)</t>
+          <t>Part-Time Data Ingest Engineer (contractor)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Digital Public Library of America</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db7fd563fd960a2d</t>
+          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ENGINEER (REMOTE OPPORTUNITY)</t>
+          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bed15d2d90e0d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer-Data Platform &amp; Analytics</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Harvestaff</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177880cf8dc57acd</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Part-Time Data Ingest Engineer (contractor)</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Digital Public Library of America</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
+          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
+          <t>Sr Software Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
+          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Harvestaff</t>
+          <t>Snap Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
+          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>QA Testing Analyst - Senior</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
+          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Software Developer</t>
+          <t>AI Engineer Senior</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
+          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Snap Inc.</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,59 +1581,59 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
+          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>QA Testing Analyst - Senior</t>
+          <t>Cybersecurity Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Engineer Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>DevCo Management</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
+          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
+          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cybersecurity Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
+          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DevCo Management</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
+          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
+          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
+          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
+          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
+          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
+          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
+          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
+          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
+          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
+          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
+          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
+          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
+          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
+          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
+          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
+          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
+          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
+          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
+          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
+          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
+          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
+          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
+          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
+          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
+          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
+          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
+          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
+          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
+          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
+          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
+          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
+          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Sr Python Developer - Onsite</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
+          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>La Mesa RV Center</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Support Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>La Mesa RV Center</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
+          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
+          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Murmuration</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Support Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,94 +3961,94 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
+          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer / SDE</t>
+          <t>Sr. Software Engineer, Java Full Stack</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>Data Analytics Engineer II - IM Enterprise Data</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Murmuration</t>
+          <t>CHRISTUS Health</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
+          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
+          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Redwood Trust</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java Full Stack</t>
+          <t>DevOps/Platform Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
+          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer II - IM Enterprise Data</t>
+          <t>AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CHRISTUS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
+          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Redwood Trust</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,29 +4161,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
+          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DevOps/Platform Engineer</t>
+          <t>Java Python Full Stack Developer Associate Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
+          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer</t>
+          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
+          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Java Python Full Stack Developer Associate Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
+          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
+          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4380,146 +4380,6 @@
         </is>
       </c>
       <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Teza Technologies</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>IonQ</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Bothell, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb417231462092a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>ICF</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>ICF</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c2b1378a08eea421</t>
         </is>

--- a/results/job_matches_2026-03-21.xlsx
+++ b/results/job_matches_2026-03-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,52 +538,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer Sr - Check Modernization and Adjustment Team</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fecb0cbc521360f</t>
+          <t>https://www.indeed.com/viewjob?jk=b695d5219c5f3d42</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer Sr - Check Modernization and Adjustment Team</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b695d5219c5f3d42</t>
+          <t>https://www.indeed.com/viewjob?jk=e13bcfee6252358d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Solutions Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hadoop, Spark, PySpark, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e13bcfee6252358d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e5351d1c126599</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer II</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hadoop, Spark, PySpark, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e5351d1c126599</t>
+          <t>https://www.indeed.com/viewjob?jk=0673331b89873626</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0673331b89873626</t>
+          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
+          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
+          <t>https://www.indeed.com/viewjob?jk=3b81ca9e34e5e9f1</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b81ca9e34e5e9f1</t>
+          <t>https://www.indeed.com/viewjob?jk=520c71629e4ae31f</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520c71629e4ae31f</t>
+          <t>https://www.indeed.com/viewjob?jk=96b820a060e96568</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b820a060e96568</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce993d8d61236e3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Software Engineer III (SWES03) DT_AI/ML</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce993d8d61236e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III (SWES03) DT_AI/ML</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cooper Standard</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Northville, MI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,69 +976,69 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=419f48f4c723af35</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cooper Standard</t>
+          <t>Independence Pet Holdings</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Northville, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=419f48f4c723af35</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a6d5ce748599c6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Independence Pet Holdings</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a6d5ce748599c6</t>
+          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>SENIOR PRODUCT ENGINEER (HYBRID CHICAGO)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c929b0d5d0c4abe8</t>
+          <t>https://www.indeed.com/viewjob?jk=db7fd563fd960a2d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>SENIOR PRODUCT ENGINEER (REMOTE OPPORTUNITY)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
+          <t>https://www.indeed.com/viewjob?jk=2bed15d2d90e0d1d</t>
         </is>
       </c>
     </row>
@@ -1168,87 +1168,87 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ENGINEER (HYBRID CHICAGO)</t>
+          <t>Data Engineer-Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db7fd563fd960a2d</t>
+          <t>https://www.indeed.com/viewjob?jk=177880cf8dc57acd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ENGINEER (REMOTE OPPORTUNITY)</t>
+          <t>Part-Time Data Ingest Engineer (contractor)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Digital Public Library of America</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bed15d2d90e0d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer-Data Platform &amp; Analytics</t>
+          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177880cf8dc57acd</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Part-Time Data Ingest Engineer (contractor)</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Digital Public Library of America</t>
+          <t>Harvestaff</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
+          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Sr Software Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Harvestaff</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
+          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Snap Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
+          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Software Developer</t>
+          <t>AI Engineer Senior</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
+          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Snap Inc.</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
+          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,59 +1476,59 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
+          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QA Testing Analyst - Senior</t>
+          <t>Cybersecurity Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, dbt, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8585f1f5e291af52</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Engineer Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>DevCo Management</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
+          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
+          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cybersecurity Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
+          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DevCo Management</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
+          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
+          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
+          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
+          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
+          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
+          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
+          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
+          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
+          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
+          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
+          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
+          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
+          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
+          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
+          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
+          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
+          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
+          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
+          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
+          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
+          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
+          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
+          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
+          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
+          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
+          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
+          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
+          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
+          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
+          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
+          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
+          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Sr Python Developer - Onsite</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
+          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>La Mesa RV Center</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Support Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>La Mesa RV Center</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
+          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,42 +3776,42 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
+          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Support Engineer</t>
+          <t>Sr. Software Engineer, Java Full Stack</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,94 +3856,94 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer / SDE</t>
+          <t>Data Analytics Engineer II - IM Enterprise Data</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>CHRISTUS Health</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Murmuration</t>
+          <t>Redwood Trust</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, MongoDB, NoSQL, ETL, CI/CD, Docker, pytest</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565e1aaf33c31830</t>
+          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java Full Stack</t>
+          <t>Java Python Full Stack Developer Associate Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
+          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer II - IM Enterprise Data</t>
+          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CHRISTUS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
+          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Redwood Trust</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
+          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DevOps/Platform Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Snowflake, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad34594ef5800a70</t>
+          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
         </is>
       </c>
     </row>
@@ -4137,251 +4137,6 @@
       <c r="G106" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Java Python Full Stack Developer Associate Software Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Teza Technologies</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>ICF</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da46c3c1cee63028</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>ICF</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b1378a08eea421</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-21.xlsx
+++ b/results/job_matches_2026-03-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Solutions Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hadoop, Spark, PySpark, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e13bcfee6252358d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e5351d1c126599</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer II</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hadoop, Spark, PySpark, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e5351d1c126599</t>
+          <t>https://www.indeed.com/viewjob?jk=0673331b89873626</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0673331b89873626</t>
+          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
+          <t>https://www.indeed.com/viewjob?jk=3b81ca9e34e5e9f1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09e481bc1c9794c</t>
+          <t>https://www.indeed.com/viewjob?jk=520c71629e4ae31f</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b81ca9e34e5e9f1</t>
+          <t>https://www.indeed.com/viewjob?jk=96b820a060e96568</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520c71629e4ae31f</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce993d8d61236e3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Software Engineer III (SWES03) DT_AI/ML</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b820a060e96568</t>
+          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Cooper Standard</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Northville, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce993d8d61236e3</t>
+          <t>https://www.indeed.com/viewjob?jk=419f48f4c723af35</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer III (SWES03) DT_AI/ML</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Independence Pet Holdings</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,54 +951,54 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a6d5ce748599c6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cooper Standard</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Northville, MI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=419f48f4c723af35</t>
+          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SENIOR PRODUCT ENGINEER (HYBRID CHICAGO)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Independence Pet Holdings</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,46 +1007,46 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a6d5ce748599c6</t>
+          <t>https://www.indeed.com/viewjob?jk=db7fd563fd960a2d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>SENIOR PRODUCT ENGINEER (REMOTE OPPORTUNITY)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
+          <t>https://www.indeed.com/viewjob?jk=2bed15d2d90e0d1d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ENGINEER (HYBRID CHICAGO)</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Cambium Learning Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db7fd563fd960a2d</t>
+          <t>https://www.indeed.com/viewjob?jk=c674b29c5cebe1e7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ENGINEER (REMOTE OPPORTUNITY)</t>
+          <t>Data Engineer-Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bed15d2d90e0d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=177880cf8dc57acd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Part-Time Data Ingest Engineer (contractor)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cambium Learning Group</t>
+          <t>Digital Public Library of America</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c674b29c5cebe1e7</t>
+          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer-Data Platform &amp; Analytics</t>
+          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177880cf8dc57acd</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Part-Time Data Ingest Engineer (contractor)</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Digital Public Library of America</t>
+          <t>Harvestaff</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
+          <t>Sr Software Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
+          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Harvestaff</t>
+          <t>Snap Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
+          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>AI Engineer Senior</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,54 +1336,54 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596c7d5d53fe3536</t>
+          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Software Developer</t>
+          <t>Cybersecurity Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Snap Inc.</t>
+          <t>DevCo Management</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1392,11 +1392,11 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
+          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Engineer Senior</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
+          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20bcf9c2d03f083c</t>
+          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cybersecurity Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
+          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DevCo Management</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
+          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
+          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
+          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
+          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
+          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
+          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
+          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
+          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
+          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
+          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
+          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
+          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
+          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
+          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
+          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
+          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
+          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
+          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
+          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
+          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
+          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
+          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
+          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
+          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
+          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
+          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
+          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
+          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
+          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
+          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
+          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
+          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
+          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Sr Python Developer - Onsite</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
+          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>La Mesa RV Center</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
+          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite</t>
+          <t>Senior Support Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Lyric</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Platform Engineer / SDE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Cambia Health Solutions</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,42 +3636,42 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
+          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,129 +3681,129 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Analytics Engineer II - IM Enterprise Data</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>La Mesa RV Center</t>
+          <t>CHRISTUS Health</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
+          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Support Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Redwood Trust</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
+          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer / SDE</t>
+          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Python Full Stack Developer Associate Software Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java Full Stack</t>
+          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdca05a9ea0e87f</t>
+          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer II - IM Enterprise Data</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CHRISTUS Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
+          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Redwood Trust</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
+          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
+          <t>AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,190 +3951,15 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Java Python Full Stack Developer Associate Software Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Teza Technologies</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>AI Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Doral, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
         </is>

--- a/results/job_matches_2026-03-21.xlsx
+++ b/results/job_matches_2026-03-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3478,17 +3478,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>La Mesa RV Center</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a28e9f2e97b7a9</t>
+          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,129 +3541,129 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa146328f582d2ee</t>
+          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Analytics Engineer II - IM Enterprise Data</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>La Mesa RV Center</t>
+          <t>CHRISTUS Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
+          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Support Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Lyric</t>
+          <t>Redwood Trust</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b994683fa99a00f</t>
+          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer / SDE</t>
+          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b53bfdd24da28f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Python Full Stack Developer Associate Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer II - IM Enterprise Data</t>
+          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CHRISTUS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
+          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Redwood Trust</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
+          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Teza Technologies</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,182 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Java Python Full Stack Developer Associate Software Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Teza Technologies</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>AI Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Doral, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb98bc0da3b1f6fd</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-21.xlsx
+++ b/results/job_matches_2026-03-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer Sr - Check Modernization and Adjustment Team</t>
+          <t>Senior Cloud and DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Bastrop, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b695d5219c5f3d42</t>
+          <t>https://www.indeed.com/viewjob?jk=fcf59ea125bfa7ff</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer II</t>
+          <t>Software Engineer Sr - Check Modernization and Adjustment Team</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hadoop, Spark, PySpark, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e5351d1c126599</t>
+          <t>https://www.indeed.com/viewjob?jk=b695d5219c5f3d42</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Data Solutions Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hadoop, Spark, PySpark, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0673331b89873626</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e5351d1c126599</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
+          <t>https://www.indeed.com/viewjob?jk=0673331b89873626</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
+          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b81ca9e34e5e9f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520c71629e4ae31f</t>
+          <t>https://www.indeed.com/viewjob?jk=3b81ca9e34e5e9f1</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b820a060e96568</t>
+          <t>https://www.indeed.com/viewjob?jk=520c71629e4ae31f</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce993d8d61236e3</t>
+          <t>https://www.indeed.com/viewjob?jk=96b820a060e96568</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer III (SWES03) DT_AI/ML</t>
+          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce993d8d61236e3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software Engineer III (SWES03) DT_AI/ML</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cooper Standard</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Northville, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,69 +906,69 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=419f48f4c723af35</t>
+          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Independence Pet Holdings</t>
+          <t>Cooper Standard</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Northville, MI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a6d5ce748599c6</t>
+          <t>https://www.indeed.com/viewjob?jk=419f48f4c723af35</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Independence Pet Holdings</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67984d7d68bde23e</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a6d5ce748599c6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ENGINEER (HYBRID CHICAGO)</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Cambium Learning Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,24 +1011,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db7fd563fd960a2d</t>
+          <t>https://www.indeed.com/viewjob?jk=c674b29c5cebe1e7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ENGINEER (REMOTE OPPORTUNITY)</t>
+          <t>SENIOR PRODUCT ENGINEER (HYBRID CHICAGO)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1051,37 +1051,37 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bed15d2d90e0d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=db7fd563fd960a2d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Engineer-Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cambium Learning Group</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c674b29c5cebe1e7</t>
+          <t>https://www.indeed.com/viewjob?jk=177880cf8dc57acd</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer-Data Platform &amp; Analytics</t>
+          <t>Part-Time Data Ingest Engineer (contractor)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Digital Public Library of America</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177880cf8dc57acd</t>
+          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Part-Time Data Ingest Engineer (contractor)</t>
+          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Digital Public Library of America</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Harvestaff</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Sr Software Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Harvestaff</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,54 +1231,54 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
+          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Software Developer</t>
+          <t>Cybersecurity Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer, Level 4 (Fixed-Term)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Snap Inc.</t>
+          <t>DevCo Management</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1287,11 +1287,11 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, ETL, Tableau, Git, Python</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae16c738518a578a</t>
+          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Engineer Senior</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e394b0856792b66</t>
+          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cybersecurity Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
+          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DevCo Management</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
+          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
+          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
+          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
+          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
+          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
+          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
+          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
+          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
+          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
+          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
+          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
+          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
+          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
+          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
+          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
+          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
+          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
+          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
+          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
+          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
+          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
+          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
+          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
+          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
+          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
+          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
+          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
+          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
+          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
+          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
+          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
+          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Sr Python Developer - Onsite</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>M-TECH SYSTEMS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
+          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>La Mesa RV Center</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,94 +3436,94 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
+          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Verinext</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, PostgreSQL, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=160c7358320627f2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>La Mesa RV Center</t>
+          <t>Redwood Trust</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer II - IM Enterprise Data</t>
+          <t>Java Python Full Stack Developer Associate Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CHRISTUS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Hadoop, HDFS, Hive, MapReduce, Impala, Spark, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec58fdfb7ee3a019</t>
+          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Redwood Trust</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
+          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,147 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Java Python Full Stack Developer Associate Software Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Teza Technologies</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29a27ecd79c8bc44</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-21.xlsx
+++ b/results/job_matches_2026-03-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer II</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,77 +626,77 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Hadoop, Spark, PySpark, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e5351d1c126599</t>
+          <t>https://www.indeed.com/viewjob?jk=0673331b89873626</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0673331b89873626</t>
+          <t>https://www.indeed.com/viewjob?jk=3b81ca9e34e5e9f1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dfd239bdcb806d</t>
+          <t>https://www.indeed.com/viewjob?jk=520c71629e4ae31f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b2dd7ad979c250</t>
+          <t>https://www.indeed.com/viewjob?jk=96b820a060e96568</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b81ca9e34e5e9f1</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce993d8d61236e3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Independence Pet Holdings</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520c71629e4ae31f</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a6d5ce748599c6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>SENIOR PRODUCT ENGINEER (HYBRID CHICAGO)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b820a060e96568</t>
+          <t>https://www.indeed.com/viewjob?jk=db7fd563fd960a2d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Cambium Learning Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,199 +881,199 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce993d8d61236e3</t>
+          <t>https://www.indeed.com/viewjob?jk=c674b29c5cebe1e7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer III (SWES03) DT_AI/ML</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mojo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1194dbf1a39e9b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f1d3e8504a06a7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software Engineers</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cooper Standard</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Northville, MI, US USA</t>
+          <t>Roseland, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Scala, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=419f48f4c723af35</t>
+          <t>https://www.indeed.com/viewjob?jk=bb04b36537a2b802</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Developer for the Office of HPD TECH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Independence Pet Holdings</t>
+          <t>New York City Department of Housing Preservation &amp; Development</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Scala, Kafka, Snowflake, ETL, ELT, dbt</t>
+          <t>S3, RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8a6d5ce748599c6</t>
+          <t>https://www.indeed.com/viewjob?jk=4ab98ea9cc28ff7b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Part-Time Data Ingest Engineer (contractor)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cambium Learning Group</t>
+          <t>Digital Public Library of America</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c674b29c5cebe1e7</t>
+          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ENGINEER (HYBRID CHICAGO)</t>
+          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db7fd563fd960a2d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer-Data Platform &amp; Analytics</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Harvestaff</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177880cf8dc57acd</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Part-Time Data Ingest Engineer (contractor)</t>
+          <t>Sr Software Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Digital Public Library of America</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,77 +1116,77 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
+          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
+          <t>Cybersecurity Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Harvestaff</t>
+          <t>DevCo Management</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
+          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Software Developer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
+          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cybersecurity Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
+          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DevCo Management</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
+          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
+          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
+          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
+          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
+          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
+          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
+          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
+          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
+          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
+          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
+          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
+          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
+          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
+          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
+          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
+          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
+          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
+          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
+          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
+          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
+          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
+          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
+          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
+          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
+          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
+          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
+          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
+          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
+          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
+          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
+          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,14 +3226,14 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
+          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
+          <t>https://www.indeed.com/viewjob?jk=5bda9e48f1024e1e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,14 +3296,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd1e9c1ff303313</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
+          <t>https://www.indeed.com/viewjob?jk=572dd86ccc7be082</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr Python Developer - Onsite</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=c071e49659e50353</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>La Mesa RV Center</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
+          <t>https://www.indeed.com/viewjob?jk=56d3332bdc3b7e53</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,102 +3436,102 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f215a50593a8ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=9127aed6ba1f03c6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Verinext</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, PostgreSQL, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=160c7358320627f2</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d981d1c9de85b5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Redwood Trust</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
+          <t>https://www.indeed.com/viewjob?jk=20ecba012dcb872c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
+          <t>https://www.indeed.com/viewjob?jk=c50789f60821a3d7</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Java Python Full Stack Developer Associate Software Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
+          <t>https://www.indeed.com/viewjob?jk=5db3e8ec7e08e1e1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,42 +3611,2002 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
+          <t>https://www.indeed.com/viewjob?jk=04ae245d423f4f15</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>AI Data Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=400f98db4bb6f73d</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=555e2360433f2c3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f40885146dec8a4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d5035a08ea5f1e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6606e12c9ff1b3b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4009b2546e8fe076</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac7f86149a2ec340</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d56d5772e687db6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50c3341377ed57a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9f65756a24c765f</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=666278eb7c24f496</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77709f84c9c6155a</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=280432393e5a110e</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e86adf0022116a65</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e612de3275e3115</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=677d6d574c5b3ec3</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5466c81ac58d34ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b330ccc7aa453c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a26e11c7ee167aed</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ec69fe49ff8d9dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=126ea7cdef071597</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73105a0a5b0d4d0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48cce4424eee2763</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eeff413ec474b08b</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Midland, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8af2618770b10440</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50b3e493edc2083f</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba3bf92b7f61bf8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7383fef92c3e822c</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46c1031df8a5a78f</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24a79838f620ae29</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff04d88198df5a34</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=801eb4fb019f4e56</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1756687393957d87</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a51ae7d37b780a38</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6a6987c98089cbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0cca6c31994af17d</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75d7d20700151ded</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c6fa018886126e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43627fd85a12efa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84ae12f4cb92ce29</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Fresno, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=662d5c581b3eff4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51d6fa2517837adc</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b66be563d1df5434</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Sr Python Developer - Onsite</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>M-TECH SYSTEMS</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Dunwoody, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Solution Architect</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>La Mesa RV Center</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>APIGEE Development Engineer</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Morris Plains, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fce9a26ec94275c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Makpar Corporation</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CloudFormation, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=644ffd1ada2946fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c258712e0383042</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc2b6b27a7b388ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30f6e0934dbdb9a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>AI Data Engineer - Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b9fddf6b4dcba23</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Verinext</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
         <v>10.4</v>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dba827c3940dc301</t>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, PostgreSQL, DynamoDB, NoSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=160c7358320627f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Redwood Trust</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>St. David's HealthCare</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a12794620257c6fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Java Python Full Stack Developer Associate Software Engineer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-21.xlsx
+++ b/results/job_matches_2026-03-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G148"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ENGINEER (HYBRID CHICAGO)</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Cambium Learning Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db7fd563fd960a2d</t>
+          <t>https://www.indeed.com/viewjob?jk=c674b29c5cebe1e7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cambium Learning Group</t>
+          <t>Mojo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c674b29c5cebe1e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f1d3e8504a06a7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>SENIOR PRODUCT ENGINEER (HYBRID CHICAGO)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mojo</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f1d3e8504a06a7</t>
+          <t>https://www.indeed.com/viewjob?jk=db7fd563fd960a2d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineers</t>
+          <t>Part-Time Data Ingest Engineer (contractor)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>Digital Public Library of America</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Roseland, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Maven, Jenkins</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb04b36537a2b802</t>
+          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Solutions Developer for the Office of HPD TECH</t>
+          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>New York City Department of Housing Preservation &amp; Development</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ab98ea9cc28ff7b</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Part-Time Data Ingest Engineer (contractor)</t>
+          <t>Mid Level Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Digital Public Library of America</t>
+          <t>Harvestaff</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chesterfield, MO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,77 +1011,77 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, PostgreSQL, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aadfffb92b106481</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
+          <t>Cybersecurity Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mid Level Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Harvestaff</t>
+          <t>DevCo Management</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1d0f6da2bd63b9</t>
+          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Software Developer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132ca3b242a8a6d5</t>
+          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cybersecurity Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Tableau, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e2c628062408c8</t>
+          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DevCo Management</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59af645ce25d5089</t>
+          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b06368bb906bdf11</t>
+          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80cde5334fb5ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fe49f7665352dc</t>
+          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21314e49acf0304c</t>
+          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1061185f3483ff2c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a8c8311c003a33d</t>
+          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05dcdaf24458670</t>
+          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb650bdebf708eea</t>
+          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9889f3265bd97b51</t>
+          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e96e5096cb81f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f226c5ea39f18f</t>
+          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=725c06692f7b1dca</t>
+          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbf7a59e180c481</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b4a2906633e183</t>
+          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e63dff37b18ed3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf00582dffe1a14</t>
+          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aba546f49aa143d5</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b650b5a85b15e4</t>
+          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f5e77bc1af1e66</t>
+          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e1ae6d45ad4d96</t>
+          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011560efb4817cea</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f95ceb673e9cbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41a069da66ebb7d</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69d39b8a42a777</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157681a9a76fa698</t>
+          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea4074f6661da1f</t>
+          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea0dcf13a007788</t>
+          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54483b40e2c149ea</t>
+          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2313bc51ab9aaa2f</t>
+          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4512d7b941e61743</t>
+          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afc1adca9797799d</t>
+          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1783da45863c66c0</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c71308b0ba7e2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17cc7f8e422e58e</t>
+          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b697785aa12cf3</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ba913deb1ede3d</t>
+          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d004ea93ba3032c8</t>
+          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e0a66343bd8d27</t>
+          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b68135a61447605</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a522a9986e6a59e6</t>
+          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5692cc1854b8b46c</t>
+          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e1fb3f6e7cd5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c5abf4c6a398d2</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc4e06430f3dc541</t>
+          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8639c6c78c5dc62a</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5e701cf86364b8</t>
+          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7437fdb72df2168d</t>
+          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf3da601f9ead51</t>
+          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69d93938154a5f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbca5902348e3774</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30141dcd872ccdd2</t>
+          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d99d79113213be6</t>
+          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed2bfe45f070a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,2492 +3121,77 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02b4cf44dcd6589</t>
+          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Verinext</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, PostgreSQL, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d303bf79c573957b</t>
+          <t>https://www.indeed.com/viewjob?jk=160c7358320627f2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI Data Engineer - Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Redwood Trust</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d236c9518fd3bff3</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Consultant</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f771042d59792429</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5bda9e48f1024e1e</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd1e9c1ff303313</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=572dd86ccc7be082</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c071e49659e50353</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56d3332bdc3b7e53</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Hermitage, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9127aed6ba1f03c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d981d1c9de85b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=20ecba012dcb872c</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Rochester, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c50789f60821a3d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Boca Raton, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5db3e8ec7e08e1e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04ae245d423f4f15</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=400f98db4bb6f73d</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Tulsa, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=555e2360433f2c3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f40885146dec8a4b</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d5035a08ea5f1e7</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6606e12c9ff1b3b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4009b2546e8fe076</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac7f86149a2ec340</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d56d5772e687db6e</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50c3341377ed57a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f65756a24c765f</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Dayton, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=666278eb7c24f496</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=77709f84c9c6155a</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=280432393e5a110e</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e86adf0022116a65</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Memphis, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e612de3275e3115</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=677d6d574c5b3ec3</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5466c81ac58d34ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b330ccc7aa453c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a26e11c7ee167aed</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec69fe49ff8d9dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Davenport, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=126ea7cdef071597</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73105a0a5b0d4d0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48cce4424eee2763</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eeff413ec474b08b</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Midland, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8af2618770b10440</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50b3e493edc2083f</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3bf92b7f61bf8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7383fef92c3e822c</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Princeton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=46c1031df8a5a78f</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24a79838f620ae29</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff04d88198df5a34</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=801eb4fb019f4e56</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1756687393957d87</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a51ae7d37b780a38</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a6987c98089cbb</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0cca6c31994af17d</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=75d7d20700151ded</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6fa018886126e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=43627fd85a12efa0</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84ae12f4cb92ce29</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Fresno, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=662d5c581b3eff4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=51d6fa2517837adc</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b66be563d1df5434</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Sr Python Developer - Onsite</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>M-TECH SYSTEMS</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Dunwoody, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, SQL Server, ELT, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f35541065e194ff3</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Solution Architect</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>La Mesa RV Center</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, ETL, ELT, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e48f0e2e494934e</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>APIGEE Development Engineer</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Morris Plains, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fce9a26ec94275c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Makpar Corporation</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CloudFormation, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=644ffd1ada2946fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c258712e0383042</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2b6b27a7b388ce</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30f6e0934dbdb9a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>AI Data Engineer - Senior Consultant</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Huntsville, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, Data Modeling, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9fddf6b4dcba23</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Verinext</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, PostgreSQL, DynamoDB, NoSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=160c7358320627f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Redwood Trust</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=8e662d0094b7e784</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>St. David's HealthCare</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a12794620257c6fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Senior Java Python Full Stack Developer -Software Engineer</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=688358c2a9b02664</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Java Python Full Stack Developer Associate Software Engineer</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80c25592f9425b10</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Java Python Full Stack Developer - Associate Software Engineer</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b6bab89238cc7fe</t>
         </is>
       </c>
     </row>
